--- a/RAMEN_FINMODEL_REAL_UA.xlsx
+++ b/RAMEN_FINMODEL_REAL_UA.xlsx
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="19">
+  <numFmts count="21">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00&quot; ₴&quot;_-;\-* #,##0.00&quot; ₴&quot;_-;_-* \-??&quot; ₴&quot;_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$₴-422]_-;\-* #,##0.00\ [$₴-422]_-;_-* \-??\ [$₴-422]_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0000&quot; €&quot;"/>
@@ -38,8 +38,10 @@
     <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
     <numFmt numFmtId="181" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
     <numFmt numFmtId="182" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
+    <numFmt numFmtId="183" formatCode="+#,##0.00&quot; ₴&quot;;-#,##0.00&quot; ₴&quot;"/>
+    <numFmt numFmtId="184" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -256,8 +258,25 @@
       <color rgb="FF172B46"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF203864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF203864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFA33A3A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="32">
     <fill>
       <patternFill/>
     </fill>
@@ -377,8 +396,43 @@
         <fgColor rgb="FFFFF4D2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB07A12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA33A3A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9A441"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC26A6A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F8FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF4DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -711,6 +765,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="11" fillId="19" borderId="10"/>
@@ -721,7 +789,7 @@
     <xf numFmtId="0" fontId="11" fillId="19" borderId="10"/>
     <xf numFmtId="9" fontId="1" fillId="19" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1138,6 +1206,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="29" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="29" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="9" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="30" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="30" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="21" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
@@ -1425,7 +1553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="71" min="1" max="1"/>
@@ -1517,10 +1645,9 @@
       <c r="D4" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" s="68" t="inlineStr">
-        <is>
-          <t>Бонус 25%; полиця = ціна партнера × 1,40.</t>
-        </is>
+      <c r="E4" s="68" t="str">
+        <f>"Бонус мережі "&amp;ROUND(D4*100,0)&amp;"%; полиця = ціна партнера × "&amp;D6&amp;"."</f>
+        <v>Бонус мережі 25%; полиця = ціна партнера × 1.4.</v>
       </c>
       <c r="F4" s="69" t="n"/>
       <c r="G4" s="69" t="n"/>
@@ -1536,13 +1663,13 @@
         </is>
       </c>
       <c r="C5" s="63" t="n"/>
-      <c r="D5" s="18" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E5" s="68" t="inlineStr">
-        <is>
-          <t>35% = (ціна партнеру − собівартість − бонус) / повна ціна партнеру.</t>
-        </is>
+      <c r="D5" s="18">
+        <f>'Цена 120 грн — 6 паллет'!C14</f>
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="68" t="str">
+        <f>ROUND(D5*100,0)&amp;"% = (ціна партнеру − собівартість − бонус) / повна ціна партнеру. Береться з аркуша «Цена 120 грн»."</f>
+        <v>30% = (ціна партнеру − собівартість − бонус) / повна ціна партнеру. Береться з аркуша «Цена 120 грн».</v>
       </c>
       <c r="F5" s="69" t="n"/>
       <c r="G5" s="69" t="n"/>
@@ -1606,12 +1733,11 @@
       <c r="C8" s="77" t="n"/>
       <c r="D8" s="23">
         <f>IF(AND(COUNT(D3:D6)=4,D3&gt;0,D4&gt;=0,D5&gt;=0,D4+D5&lt;1,D6&gt;0),1-D4-D5,NA())</f>
-        <v>0.4</v>
-      </c>
-      <c r="E8" s="79" t="inlineStr">
-        <is>
-          <t>100% − бонус − маржа. За поточних умов: 100% − 25% − 35% = 40%.</t>
-        </is>
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="79" t="str">
+        <f>"100% − бонус − маржа. За поточних умов: 100% − "&amp;ROUND(D4*100,0)&amp;"% − "&amp;ROUND(D5*100,0)&amp;"% = "&amp;ROUND(D8*100,0)&amp;"%."</f>
+        <v>100% − бонус − маржа. За поточних умов: 100% − 25% − 30% = 45%.</v>
       </c>
       <c r="F8" s="69" t="n"/>
       <c r="G8" s="69" t="n"/>
@@ -1892,23 +2018,23 @@
       </c>
       <c r="G11" s="9">
         <f>F11/$D$8</f>
-        <v>167.49</v>
+        <v>148.88000000000002</v>
       </c>
       <c r="H11" s="10">
         <f>G11*$D$4</f>
-        <v>41.8725</v>
+        <v>37.220000000000006</v>
       </c>
       <c r="I11" s="11">
         <f>G11-F11-H11</f>
-        <v>58.6215</v>
+        <v>44.66400000000001</v>
       </c>
       <c r="J11" s="12">
         <f>I11/G11</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K11" s="13">
         <f>G11*$D$6</f>
-        <v>234.486</v>
+        <v>208.43200000000002</v>
       </c>
       <c r="L11" s="14">
         <f>F11/(1-$D$4)</f>
@@ -1920,11 +2046,11 @@
       </c>
       <c r="N11" s="15">
         <f>G11-F11</f>
-        <v>100.494</v>
+        <v>81.88400000000001</v>
       </c>
       <c r="O11" s="16">
         <f>N11-H11</f>
-        <v>58.6215</v>
+        <v>44.66400000000001</v>
       </c>
       <c r="P11" s="40">
         <f>$F11/(1-$D$4-$P$9)</f>
@@ -2033,23 +2159,23 @@
       </c>
       <c r="G12" s="9">
         <f>F12/$D$8</f>
-        <v>167.49</v>
+        <v>148.88000000000002</v>
       </c>
       <c r="H12" s="10">
         <f>G12*$D$4</f>
-        <v>41.8725</v>
+        <v>37.220000000000006</v>
       </c>
       <c r="I12" s="11">
         <f>G12-F12-H12</f>
-        <v>58.6215</v>
+        <v>44.66400000000001</v>
       </c>
       <c r="J12" s="12">
         <f>I12/G12</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K12" s="13">
         <f>G12*$D$6</f>
-        <v>234.486</v>
+        <v>208.43200000000002</v>
       </c>
       <c r="L12" s="14">
         <f>F12/(1-$D$4)</f>
@@ -2061,11 +2187,11 @@
       </c>
       <c r="N12" s="15">
         <f>G12-F12</f>
-        <v>100.494</v>
+        <v>81.88400000000001</v>
       </c>
       <c r="O12" s="16">
         <f>N12-H12</f>
-        <v>58.6215</v>
+        <v>44.66400000000001</v>
       </c>
       <c r="P12" s="40">
         <f>$F12/(1-$D$4-$P$9)</f>
@@ -2174,23 +2300,23 @@
       </c>
       <c r="G13" s="9">
         <f>F13/$D$8</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="H13" s="10">
         <f>G13*$D$4</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="I13" s="11">
         <f>G13-F13-H13</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="J13" s="12">
         <f>I13/G13</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K13" s="13">
         <f>G13*$D$6</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="L13" s="14">
         <f>F13/(1-$D$4)</f>
@@ -2202,11 +2328,11 @@
       </c>
       <c r="N13" s="15">
         <f>G13-F13</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="O13" s="16">
         <f>N13-H13</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="P13" s="40">
         <f>$F13/(1-$D$4-$P$9)</f>
@@ -2315,23 +2441,23 @@
       </c>
       <c r="G14" s="9">
         <f>F14/$D$8</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="H14" s="10">
         <f>G14*$D$4</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="I14" s="11">
         <f>G14-F14-H14</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="J14" s="12">
         <f>I14/G14</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K14" s="13">
         <f>G14*$D$6</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="L14" s="14">
         <f>F14/(1-$D$4)</f>
@@ -2343,11 +2469,11 @@
       </c>
       <c r="N14" s="15">
         <f>G14-F14</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="O14" s="16">
         <f>N14-H14</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="P14" s="40">
         <f>$F14/(1-$D$4-$P$9)</f>
@@ -2456,23 +2582,23 @@
       </c>
       <c r="G15" s="9">
         <f>F15/$D$8</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="H15" s="10">
         <f>G15*$D$4</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="I15" s="11">
         <f>G15-F15-H15</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="J15" s="12">
         <f>I15/G15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="13">
         <f>G15*$D$6</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="L15" s="14">
         <f>F15/(1-$D$4)</f>
@@ -2484,11 +2610,11 @@
       </c>
       <c r="N15" s="15">
         <f>G15-F15</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="O15" s="16">
         <f>N15-H15</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="P15" s="40">
         <f>$F15/(1-$D$4-$P$9)</f>
@@ -2597,23 +2723,23 @@
       </c>
       <c r="G16" s="9">
         <f>F16/$D$8</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="H16" s="10">
         <f>G16*$D$4</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="I16" s="11">
         <f>G16-F16-H16</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="J16" s="12">
         <f>I16/G16</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K16" s="13">
         <f>G16*$D$6</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="L16" s="14">
         <f>F16/(1-$D$4)</f>
@@ -2625,11 +2751,11 @@
       </c>
       <c r="N16" s="15">
         <f>G16-F16</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="O16" s="16">
         <f>N16-H16</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="P16" s="40">
         <f>$F16/(1-$D$4-$P$9)</f>
@@ -3032,27 +3158,27 @@
       <c r="E28" s="65" t="n"/>
       <c r="F28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" ht="31.05" customHeight="1" s="71">
@@ -3073,27 +3199,27 @@
       <c r="E29" s="65" t="n"/>
       <c r="F29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" ht="31.05" customHeight="1" s="71">
@@ -3114,27 +3240,27 @@
       <c r="E30" s="65" t="n"/>
       <c r="F30" s="34">
         <f>G11</f>
-        <v>167.49</v>
+        <v>148.88000000000002</v>
       </c>
       <c r="G30" s="34">
         <f>G12</f>
-        <v>167.49</v>
+        <v>148.88000000000002</v>
       </c>
       <c r="H30" s="34">
         <f>G13</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="I30" s="34">
         <f>G14</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="J30" s="34">
         <f>G15</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
       <c r="K30" s="34">
         <f>G16</f>
-        <v>145.158</v>
+        <v>129.0293333333333</v>
       </c>
     </row>
     <row r="31" ht="31.05" customHeight="1" s="71">
@@ -3155,27 +3281,27 @@
       <c r="E31" s="65" t="n"/>
       <c r="F31" s="31">
         <f>N11</f>
-        <v>100.494</v>
+        <v>81.88400000000001</v>
       </c>
       <c r="G31" s="31">
         <f>N12</f>
-        <v>100.494</v>
+        <v>81.88400000000001</v>
       </c>
       <c r="H31" s="31">
         <f>N13</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="I31" s="31">
         <f>N14</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="J31" s="31">
         <f>N15</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
       <c r="K31" s="31">
         <f>N16</f>
-        <v>87.09479999999999</v>
+        <v>70.96613333333332</v>
       </c>
     </row>
     <row r="32" ht="31.05" customHeight="1" s="71">
@@ -3196,27 +3322,27 @@
       <c r="E32" s="65" t="n"/>
       <c r="F32" s="31">
         <f>H11</f>
-        <v>41.8725</v>
+        <v>37.220000000000006</v>
       </c>
       <c r="G32" s="31">
         <f>H12</f>
-        <v>41.8725</v>
+        <v>37.220000000000006</v>
       </c>
       <c r="H32" s="31">
         <f>H13</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="I32" s="31">
         <f>H14</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="J32" s="31">
         <f>H15</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
       <c r="K32" s="31">
         <f>H16</f>
-        <v>36.2895</v>
+        <v>32.25733333333333</v>
       </c>
     </row>
     <row r="33" ht="31.05" customHeight="1" s="71">
@@ -3237,27 +3363,27 @@
       <c r="E33" s="65" t="n"/>
       <c r="F33" s="36">
         <f>I11</f>
-        <v>58.6215</v>
+        <v>44.66400000000001</v>
       </c>
       <c r="G33" s="36">
         <f>I12</f>
-        <v>58.6215</v>
+        <v>44.66400000000001</v>
       </c>
       <c r="H33" s="36">
         <f>I13</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="I33" s="36">
         <f>I14</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="J33" s="36">
         <f>I15</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
       <c r="K33" s="36">
         <f>I16</f>
-        <v>50.805299999999995</v>
+        <v>38.70879999999999</v>
       </c>
     </row>
     <row r="34" ht="31.05" customHeight="1" s="71">
@@ -3278,27 +3404,27 @@
       <c r="E34" s="65" t="n"/>
       <c r="F34" s="37">
         <f>J11</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="37">
         <f>J12</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H34" s="37">
         <f>J13</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I34" s="37">
         <f>J14</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J34" s="37">
         <f>J15</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="37">
         <f>J16</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35" ht="31.05" customHeight="1" s="71">
@@ -3401,27 +3527,27 @@
       <c r="E37" s="65" t="n"/>
       <c r="F37" s="34">
         <f>K11</f>
-        <v>234.486</v>
+        <v>208.43200000000002</v>
       </c>
       <c r="G37" s="34">
         <f>K12</f>
-        <v>234.486</v>
+        <v>208.43200000000002</v>
       </c>
       <c r="H37" s="34">
         <f>K13</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="I37" s="34">
         <f>K14</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="J37" s="34">
         <f>K15</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
       <c r="K37" s="34">
         <f>K16</f>
-        <v>203.22119999999998</v>
+        <v>180.64106666666663</v>
       </c>
     </row>
     <row r="38" ht="31.05" customHeight="1" s="71">
@@ -3506,20 +3632,605 @@
         <v>108.38463999999999</v>
       </c>
     </row>
+    <row r="42" ht="26" customHeight="1" s="71">
+      <c r="B42" s="152" t="inlineStr">
+        <is>
+          <t>ДО → ПІСЛЯ · ціна на полиці при поточній закупівлі та при запиті SIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="71">
+      <c r="B43" s="153" t="str">
+        <f>"Бонус мережі "&amp;ROUND('Цена 120 грн — 6 паллет'!D14*100,0)&amp;" % · маржа "&amp;ROUND('Цена 120 грн — 6 паллет'!C14*100,0)&amp;" % · націнка ×"&amp;'Цена 120 грн — 6 паллет'!E14</f>
+        <v>Бонус мережі 25 % · маржа 30 % · націнка ×1.4</v>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1" s="71">
+      <c r="E44" s="154" t="inlineStr">
+        <is>
+          <t>ДО · поточна закупівля SIAS</t>
+        </is>
+      </c>
+      <c r="F44" s="154" t="n"/>
+      <c r="G44" s="154" t="n"/>
+      <c r="H44" s="154" t="n"/>
+      <c r="I44" s="154" t="n"/>
+      <c r="J44" s="154" t="n"/>
+      <c r="K44" s="155" t="inlineStr">
+        <is>
+          <t>ПІСЛЯ · запит SIAS (одна ціна на 6 SKU)</t>
+        </is>
+      </c>
+      <c r="L44" s="155" t="n"/>
+      <c r="M44" s="155" t="n"/>
+      <c r="N44" s="155" t="n"/>
+      <c r="O44" s="155" t="n"/>
+      <c r="P44" s="155" t="n"/>
+      <c r="Q44" s="156" t="inlineStr">
+        <is>
+          <t>ЗМІНА</t>
+        </is>
+      </c>
+      <c r="R44" s="156" t="n"/>
+    </row>
+    <row r="45" ht="42" customHeight="1" s="71">
+      <c r="A45" s="157" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B45" s="157" t="inlineStr">
+        <is>
+          <t>Позиція</t>
+        </is>
+      </c>
+      <c r="C45" s="157" t="inlineStr">
+        <is>
+          <t>Закупівля SIAS: до → після</t>
+        </is>
+      </c>
+      <c r="D45" s="157" t="inlineStr">
+        <is>
+          <t>Вага, г</t>
+        </is>
+      </c>
+      <c r="E45" s="158" t="inlineStr">
+        <is>
+          <t>Закупівля, €/пач.</t>
+        </is>
+      </c>
+      <c r="F45" s="158" t="inlineStr">
+        <is>
+          <t>СС, ₴/пач.</t>
+        </is>
+      </c>
+      <c r="G45" s="158" t="inlineStr">
+        <is>
+          <t>Ціна партнеру, ₴</t>
+        </is>
+      </c>
+      <c r="H45" s="158" t="inlineStr">
+        <is>
+          <t>Бонус мережі, ₴</t>
+        </is>
+      </c>
+      <c r="I45" s="158" t="inlineStr">
+        <is>
+          <t>Залишається після бонусу, ₴</t>
+        </is>
+      </c>
+      <c r="J45" s="158" t="inlineStr">
+        <is>
+          <t>Полиця з ПДВ, ₴</t>
+        </is>
+      </c>
+      <c r="K45" s="159" t="inlineStr">
+        <is>
+          <t>Закупівля, €/пач.</t>
+        </is>
+      </c>
+      <c r="L45" s="159" t="inlineStr">
+        <is>
+          <t>СС, ₴/пач.</t>
+        </is>
+      </c>
+      <c r="M45" s="159" t="inlineStr">
+        <is>
+          <t>Ціна партнеру, ₴</t>
+        </is>
+      </c>
+      <c r="N45" s="159" t="inlineStr">
+        <is>
+          <t>Бонус мережі, ₴</t>
+        </is>
+      </c>
+      <c r="O45" s="159" t="inlineStr">
+        <is>
+          <t>Залишається після бонусу, ₴</t>
+        </is>
+      </c>
+      <c r="P45" s="159" t="inlineStr">
+        <is>
+          <t>Полиця з ПДВ, ₴</t>
+        </is>
+      </c>
+      <c r="Q45" s="160" t="inlineStr">
+        <is>
+          <t>Δ полиці, ₴</t>
+        </is>
+      </c>
+      <c r="R45" s="160" t="inlineStr">
+        <is>
+          <t>Δ полиці, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1" s="71">
+      <c r="A46" s="161">
+        <f>A11</f>
+        <v>1</v>
+      </c>
+      <c r="B46" s="162" t="str">
+        <f>C11</f>
+        <v>Gouda Cheese 123 г</v>
+      </c>
+      <c r="C46" s="161" t="str">
+        <f>"€"&amp;ROUND(E46,2)&amp;" → €"&amp;ROUND(K46,2)</f>
+        <v>€0.75 → €0.32</v>
+      </c>
+      <c r="D46" s="161">
+        <f>D11</f>
+        <v>123</v>
+      </c>
+      <c r="E46" s="163">
+        <f>'Цена 120 грн — 6 паллет'!$B$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="F46" s="164">
+        <f>F11</f>
+        <v>66.99600000000001</v>
+      </c>
+      <c r="G46" s="164">
+        <f>G11</f>
+        <v>148.88000000000002</v>
+      </c>
+      <c r="H46" s="164">
+        <f>H11</f>
+        <v>37.220000000000006</v>
+      </c>
+      <c r="I46" s="164">
+        <f>I11</f>
+        <v>44.66400000000001</v>
+      </c>
+      <c r="J46" s="165">
+        <f>K11</f>
+        <v>208.43200000000002</v>
+      </c>
+      <c r="K46" s="166">
+        <f>'Цена 120 грн — 6 паллет'!$B$20</f>
+        <v>0.32</v>
+      </c>
+      <c r="L46" s="167">
+        <f>'Цена 120 грн — 6 паллет'!$C$8</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="M46" s="167">
+        <f>L46/(1-$D$4-$D$5)</f>
+        <v>84.79893333333332</v>
+      </c>
+      <c r="N46" s="167">
+        <f>M46*$D$4</f>
+        <v>21.19973333333333</v>
+      </c>
+      <c r="O46" s="167">
+        <f>M46-L46-N46</f>
+        <v>25.43968</v>
+      </c>
+      <c r="P46" s="168">
+        <f>M46*$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="Q46" s="169">
+        <f>P46-J46</f>
+        <v>-89.71349333333337</v>
+      </c>
+      <c r="R46" s="170">
+        <f>Q46/J46</f>
+        <v>-0.4304209206519794</v>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1" s="71">
+      <c r="A47" s="161">
+        <f>A12</f>
+        <v>2</v>
+      </c>
+      <c r="B47" s="162" t="str">
+        <f>C12</f>
+        <v>Carbonara Spicy 131 г</v>
+      </c>
+      <c r="C47" s="161" t="str">
+        <f>"€"&amp;ROUND(E47,2)&amp;" → €"&amp;ROUND(K47,2)</f>
+        <v>€0.75 → €0.32</v>
+      </c>
+      <c r="D47" s="161">
+        <f>D12</f>
+        <v>131</v>
+      </c>
+      <c r="E47" s="163">
+        <f>'Цена 120 грн — 6 паллет'!$B$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="F47" s="164">
+        <f>F12</f>
+        <v>66.99600000000001</v>
+      </c>
+      <c r="G47" s="164">
+        <f>G12</f>
+        <v>148.88000000000002</v>
+      </c>
+      <c r="H47" s="164">
+        <f>H12</f>
+        <v>37.220000000000006</v>
+      </c>
+      <c r="I47" s="164">
+        <f>I12</f>
+        <v>44.66400000000001</v>
+      </c>
+      <c r="J47" s="165">
+        <f>K12</f>
+        <v>208.43200000000002</v>
+      </c>
+      <c r="K47" s="166">
+        <f>'Цена 120 грн — 6 паллет'!$B$20</f>
+        <v>0.32</v>
+      </c>
+      <c r="L47" s="167">
+        <f>'Цена 120 грн — 6 паллет'!$C$8</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="M47" s="167">
+        <f>L47/(1-$D$4-$D$5)</f>
+        <v>84.79893333333332</v>
+      </c>
+      <c r="N47" s="167">
+        <f>M47*$D$4</f>
+        <v>21.19973333333333</v>
+      </c>
+      <c r="O47" s="167">
+        <f>M47-L47-N47</f>
+        <v>25.43968</v>
+      </c>
+      <c r="P47" s="168">
+        <f>M47*$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="Q47" s="169">
+        <f>P47-J47</f>
+        <v>-89.71349333333337</v>
+      </c>
+      <c r="R47" s="170">
+        <f>Q47/J47</f>
+        <v>-0.4304209206519794</v>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1" s="71">
+      <c r="A48" s="161">
+        <f>A13</f>
+        <v>3</v>
+      </c>
+      <c r="B48" s="162" t="str">
+        <f>C13</f>
+        <v>Vegetable Flavor 113 г</v>
+      </c>
+      <c r="C48" s="161" t="str">
+        <f>"€"&amp;ROUND(E48,2)&amp;" → €"&amp;ROUND(K48,2)</f>
+        <v>€0.65 → €0.32</v>
+      </c>
+      <c r="D48" s="161">
+        <f>D13</f>
+        <v>113</v>
+      </c>
+      <c r="E48" s="163">
+        <f>'Цена 120 грн — 6 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F48" s="164">
+        <f>F13</f>
+        <v>58.063199999999995</v>
+      </c>
+      <c r="G48" s="164">
+        <f>G13</f>
+        <v>129.0293333333333</v>
+      </c>
+      <c r="H48" s="164">
+        <f>H13</f>
+        <v>32.25733333333333</v>
+      </c>
+      <c r="I48" s="164">
+        <f>I13</f>
+        <v>38.70879999999999</v>
+      </c>
+      <c r="J48" s="165">
+        <f>K13</f>
+        <v>180.64106666666663</v>
+      </c>
+      <c r="K48" s="166">
+        <f>'Цена 120 грн — 6 паллет'!$B$20</f>
+        <v>0.32</v>
+      </c>
+      <c r="L48" s="167">
+        <f>'Цена 120 грн — 6 паллет'!$C$8</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="M48" s="167">
+        <f>L48/(1-$D$4-$D$5)</f>
+        <v>84.79893333333332</v>
+      </c>
+      <c r="N48" s="167">
+        <f>M48*$D$4</f>
+        <v>21.19973333333333</v>
+      </c>
+      <c r="O48" s="167">
+        <f>M48-L48-N48</f>
+        <v>25.43968</v>
+      </c>
+      <c r="P48" s="168">
+        <f>M48*$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="Q48" s="169">
+        <f>P48-J48</f>
+        <v>-61.92255999999999</v>
+      </c>
+      <c r="R48" s="170">
+        <f>Q48/J48</f>
+        <v>-0.342793369983053</v>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1" s="71">
+      <c r="A49" s="161">
+        <f>A14</f>
+        <v>4</v>
+      </c>
+      <c r="B49" s="162" t="str">
+        <f>C14</f>
+        <v>Spicy Flavor 112.5 г</v>
+      </c>
+      <c r="C49" s="161" t="str">
+        <f>"€"&amp;ROUND(E49,2)&amp;" → €"&amp;ROUND(K49,2)</f>
+        <v>€0.65 → €0.32</v>
+      </c>
+      <c r="D49" s="161">
+        <f>D14</f>
+        <v>112.5</v>
+      </c>
+      <c r="E49" s="163">
+        <f>'Цена 120 грн — 6 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F49" s="164">
+        <f>F14</f>
+        <v>58.063199999999995</v>
+      </c>
+      <c r="G49" s="164">
+        <f>G14</f>
+        <v>129.0293333333333</v>
+      </c>
+      <c r="H49" s="164">
+        <f>H14</f>
+        <v>32.25733333333333</v>
+      </c>
+      <c r="I49" s="164">
+        <f>I14</f>
+        <v>38.70879999999999</v>
+      </c>
+      <c r="J49" s="165">
+        <f>K14</f>
+        <v>180.64106666666663</v>
+      </c>
+      <c r="K49" s="166">
+        <f>'Цена 120 грн — 6 паллет'!$B$20</f>
+        <v>0.32</v>
+      </c>
+      <c r="L49" s="167">
+        <f>'Цена 120 грн — 6 паллет'!$C$8</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="M49" s="167">
+        <f>L49/(1-$D$4-$D$5)</f>
+        <v>84.79893333333332</v>
+      </c>
+      <c r="N49" s="167">
+        <f>M49*$D$4</f>
+        <v>21.19973333333333</v>
+      </c>
+      <c r="O49" s="167">
+        <f>M49-L49-N49</f>
+        <v>25.43968</v>
+      </c>
+      <c r="P49" s="168">
+        <f>M49*$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="Q49" s="169">
+        <f>P49-J49</f>
+        <v>-61.92255999999999</v>
+      </c>
+      <c r="R49" s="170">
+        <f>Q49/J49</f>
+        <v>-0.342793369983053</v>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1" s="71">
+      <c r="A50" s="161">
+        <f>A15</f>
+        <v>5</v>
+      </c>
+      <c r="B50" s="162" t="str">
+        <f>C15</f>
+        <v>Beef Flavor 113 г</v>
+      </c>
+      <c r="C50" s="161" t="str">
+        <f>"€"&amp;ROUND(E50,2)&amp;" → €"&amp;ROUND(K50,2)</f>
+        <v>€0.65 → €0.32</v>
+      </c>
+      <c r="D50" s="161">
+        <f>D15</f>
+        <v>113</v>
+      </c>
+      <c r="E50" s="163">
+        <f>'Цена 120 грн — 6 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F50" s="164">
+        <f>F15</f>
+        <v>58.063199999999995</v>
+      </c>
+      <c r="G50" s="164">
+        <f>G15</f>
+        <v>129.0293333333333</v>
+      </c>
+      <c r="H50" s="164">
+        <f>H15</f>
+        <v>32.25733333333333</v>
+      </c>
+      <c r="I50" s="164">
+        <f>I15</f>
+        <v>38.70879999999999</v>
+      </c>
+      <c r="J50" s="165">
+        <f>K15</f>
+        <v>180.64106666666663</v>
+      </c>
+      <c r="K50" s="166">
+        <f>'Цена 120 грн — 6 паллет'!$B$20</f>
+        <v>0.32</v>
+      </c>
+      <c r="L50" s="167">
+        <f>'Цена 120 грн — 6 паллет'!$C$8</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="M50" s="167">
+        <f>L50/(1-$D$4-$D$5)</f>
+        <v>84.79893333333332</v>
+      </c>
+      <c r="N50" s="167">
+        <f>M50*$D$4</f>
+        <v>21.19973333333333</v>
+      </c>
+      <c r="O50" s="167">
+        <f>M50-L50-N50</f>
+        <v>25.43968</v>
+      </c>
+      <c r="P50" s="168">
+        <f>M50*$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="Q50" s="169">
+        <f>P50-J50</f>
+        <v>-61.92255999999999</v>
+      </c>
+      <c r="R50" s="170">
+        <f>Q50/J50</f>
+        <v>-0.342793369983053</v>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1" s="71">
+      <c r="A51" s="161">
+        <f>A16</f>
+        <v>6</v>
+      </c>
+      <c r="B51" s="162" t="str">
+        <f>C16</f>
+        <v>Chicken Flavor 113 г</v>
+      </c>
+      <c r="C51" s="161" t="str">
+        <f>"€"&amp;ROUND(E51,2)&amp;" → €"&amp;ROUND(K51,2)</f>
+        <v>€0.65 → €0.32</v>
+      </c>
+      <c r="D51" s="161">
+        <f>D16</f>
+        <v>113</v>
+      </c>
+      <c r="E51" s="163">
+        <f>'Цена 120 грн — 6 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F51" s="164">
+        <f>F16</f>
+        <v>58.063199999999995</v>
+      </c>
+      <c r="G51" s="164">
+        <f>G16</f>
+        <v>129.0293333333333</v>
+      </c>
+      <c r="H51" s="164">
+        <f>H16</f>
+        <v>32.25733333333333</v>
+      </c>
+      <c r="I51" s="164">
+        <f>I16</f>
+        <v>38.70879999999999</v>
+      </c>
+      <c r="J51" s="165">
+        <f>K16</f>
+        <v>180.64106666666663</v>
+      </c>
+      <c r="K51" s="166">
+        <f>'Цена 120 грн — 6 паллет'!$B$20</f>
+        <v>0.32</v>
+      </c>
+      <c r="L51" s="167">
+        <f>'Цена 120 грн — 6 паллет'!$C$8</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="M51" s="167">
+        <f>L51/(1-$D$4-$D$5)</f>
+        <v>84.79893333333332</v>
+      </c>
+      <c r="N51" s="167">
+        <f>M51*$D$4</f>
+        <v>21.19973333333333</v>
+      </c>
+      <c r="O51" s="167">
+        <f>M51-L51-N51</f>
+        <v>25.43968</v>
+      </c>
+      <c r="P51" s="168">
+        <f>M51*$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="Q51" s="169">
+        <f>P51-J51</f>
+        <v>-61.92255999999999</v>
+      </c>
+      <c r="R51" s="170">
+        <f>Q51/J51</f>
+        <v>-0.342793369983053</v>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1" s="71">
+      <c r="B53" s="171" t="inlineStr">
+        <is>
+          <t>СС «до» — реальна (Self-Cost), «після» — розрахунок на запит SIAS (логістика рівномірно на пачку). Бонус, маржа та націнка — з аркуша «Цена 120 грн».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="69">
     <mergeCell ref="U9:Y9"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D34:E34"/>
+    <mergeCell ref="K44:P44"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="E7:K7"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="P9:T9"/>
     <mergeCell ref="D21:E21"/>
@@ -3528,22 +4239,27 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B43:R43"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B42:R42"/>
+    <mergeCell ref="E44:J44"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E5:K5"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B53:R53"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="E4:K4"/>
     <mergeCell ref="D28:E28"/>
+    <mergeCell ref="Q44:R44"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="AE9:AI9"/>
     <mergeCell ref="D39:E39"/>
@@ -3579,7 +4295,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AI59" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:AI73" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3590,7 +4306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="71" min="1" max="1"/>
@@ -3682,10 +4398,9 @@
       <c r="D4" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" s="68" t="inlineStr">
-        <is>
-          <t>Бонус 25%; полиця = ціна партнера × 1,40.</t>
-        </is>
+      <c r="E4" s="68" t="str">
+        <f>"Бонус мережі "&amp;ROUND(D4*100,0)&amp;"%; полиця = ціна партнера × "&amp;D6&amp;"."</f>
+        <v>Бонус мережі 25%; полиця = ціна партнера × 1.4.</v>
       </c>
       <c r="F4" s="69" t="n"/>
       <c r="G4" s="69" t="n"/>
@@ -3701,13 +4416,13 @@
         </is>
       </c>
       <c r="C5" s="63" t="n"/>
-      <c r="D5" s="18" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E5" s="68" t="inlineStr">
-        <is>
-          <t>35% = (ціна партнеру − собівартість − бонус) / повна ціна партнеру.</t>
-        </is>
+      <c r="D5" s="18">
+        <f>'Цена 120 грн — 33 паллет'!C14</f>
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="68" t="str">
+        <f>ROUND(D5*100,0)&amp;"% = (ціна партнеру − собівартість − бонус) / повна ціна партнеру. Береться з аркуша «Цена 120 грн»."</f>
+        <v>30% = (ціна партнеру − собівартість − бонус) / повна ціна партнеру. Береться з аркуша «Цена 120 грн».</v>
       </c>
       <c r="F5" s="69" t="n"/>
       <c r="G5" s="69" t="n"/>
@@ -3771,12 +4486,11 @@
       <c r="C8" s="77" t="n"/>
       <c r="D8" s="23">
         <f>IF(AND(COUNT(D3:D6)=4,D3&gt;0,D4&gt;=0,D5&gt;=0,D4+D5&lt;1,D6&gt;0),1-D4-D5,NA())</f>
-        <v>0.4</v>
-      </c>
-      <c r="E8" s="79" t="inlineStr">
-        <is>
-          <t>100% − бонус − маржа. За поточних умов: 100% − 25% − 35% = 40%.</t>
-        </is>
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="79" t="str">
+        <f>"100% − бонус − маржа. За поточних умов: 100% − "&amp;ROUND(D4*100,0)&amp;"% − "&amp;ROUND(D5*100,0)&amp;"% = "&amp;ROUND(D8*100,0)&amp;"%."</f>
+        <v>100% − бонус − маржа. За поточних умов: 100% − 25% − 30% = 45%.</v>
       </c>
       <c r="F8" s="69" t="n"/>
       <c r="G8" s="69" t="n"/>
@@ -4057,23 +4771,23 @@
       </c>
       <c r="G11" s="9">
         <f>F11/$D$8</f>
-        <v>130.32078774617062</v>
+        <v>115.84070021881833</v>
       </c>
       <c r="H11" s="10">
         <f>G11*$D$4</f>
-        <v>32.580196936542656</v>
+        <v>28.96017505470458</v>
       </c>
       <c r="I11" s="11">
         <f>G11-F11-H11</f>
-        <v>45.61227571115972</v>
+        <v>34.7522100656455</v>
       </c>
       <c r="J11" s="12">
         <f>I11/G11</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K11" s="13">
         <f>G11*$D$6</f>
-        <v>182.44910284463887</v>
+        <v>162.17698030634565</v>
       </c>
       <c r="L11" s="14">
         <f>F11/(1-$D$4)</f>
@@ -4085,11 +4799,11 @@
       </c>
       <c r="N11" s="15">
         <f>G11-F11</f>
-        <v>78.19247264770237</v>
+        <v>63.71238512035008</v>
       </c>
       <c r="O11" s="16">
         <f>N11-H11</f>
-        <v>45.61227571115972</v>
+        <v>34.7522100656455</v>
       </c>
       <c r="P11" s="40">
         <f>$F11/(1-$D$4-$P$9)</f>
@@ -4198,23 +4912,23 @@
       </c>
       <c r="G12" s="9">
         <f>F12/$D$8</f>
-        <v>130.32078774617062</v>
+        <v>115.84070021881833</v>
       </c>
       <c r="H12" s="10">
         <f>G12*$D$4</f>
-        <v>32.580196936542656</v>
+        <v>28.96017505470458</v>
       </c>
       <c r="I12" s="11">
         <f>G12-F12-H12</f>
-        <v>45.61227571115972</v>
+        <v>34.7522100656455</v>
       </c>
       <c r="J12" s="12">
         <f>I12/G12</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K12" s="13">
         <f>G12*$D$6</f>
-        <v>182.44910284463887</v>
+        <v>162.17698030634565</v>
       </c>
       <c r="L12" s="14">
         <f>F12/(1-$D$4)</f>
@@ -4226,11 +4940,11 @@
       </c>
       <c r="N12" s="15">
         <f>G12-F12</f>
-        <v>78.19247264770237</v>
+        <v>63.71238512035008</v>
       </c>
       <c r="O12" s="16">
         <f>N12-H12</f>
-        <v>45.61227571115972</v>
+        <v>34.7522100656455</v>
       </c>
       <c r="P12" s="40">
         <f>$F12/(1-$D$4-$P$9)</f>
@@ -4339,23 +5053,23 @@
       </c>
       <c r="G13" s="9">
         <f>F13/$D$8</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="H13" s="10">
         <f>G13*$D$4</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="I13" s="11">
         <f>G13-F13-H13</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="J13" s="12">
         <f>I13/G13</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="K13" s="13">
         <f>G13*$D$6</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="L13" s="14">
         <f>F13/(1-$D$4)</f>
@@ -4367,11 +5081,11 @@
       </c>
       <c r="N13" s="15">
         <f>G13-F13</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="O13" s="16">
         <f>N13-H13</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="P13" s="40">
         <f>$F13/(1-$D$4-$P$9)</f>
@@ -4480,23 +5194,23 @@
       </c>
       <c r="G14" s="9">
         <f>F14/$D$8</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="H14" s="10">
         <f>G14*$D$4</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="I14" s="11">
         <f>G14-F14-H14</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="J14" s="12">
         <f>I14/G14</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="K14" s="13">
         <f>G14*$D$6</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="L14" s="14">
         <f>F14/(1-$D$4)</f>
@@ -4508,11 +5222,11 @@
       </c>
       <c r="N14" s="15">
         <f>G14-F14</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="O14" s="16">
         <f>N14-H14</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="P14" s="40">
         <f>$F14/(1-$D$4-$P$9)</f>
@@ -4621,23 +5335,23 @@
       </c>
       <c r="G15" s="9">
         <f>F15/$D$8</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="H15" s="10">
         <f>G15*$D$4</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="I15" s="11">
         <f>G15-F15-H15</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="J15" s="12">
         <f>I15/G15</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="K15" s="13">
         <f>G15*$D$6</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="L15" s="14">
         <f>F15/(1-$D$4)</f>
@@ -4649,11 +5363,11 @@
       </c>
       <c r="N15" s="15">
         <f>G15-F15</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="O15" s="16">
         <f>N15-H15</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="P15" s="40">
         <f>$F15/(1-$D$4-$P$9)</f>
@@ -4762,23 +5476,23 @@
       </c>
       <c r="G16" s="9">
         <f>F16/$D$8</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="H16" s="10">
         <f>G16*$D$4</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="I16" s="11">
         <f>G16-F16-H16</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="J16" s="12">
         <f>I16/G16</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="K16" s="13">
         <f>G16*$D$6</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="L16" s="14">
         <f>F16/(1-$D$4)</f>
@@ -4790,11 +5504,11 @@
       </c>
       <c r="N16" s="15">
         <f>G16-F16</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="O16" s="16">
         <f>N16-H16</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="P16" s="40">
         <f>$F16/(1-$D$4-$P$9)</f>
@@ -5197,27 +5911,27 @@
       <c r="E28" s="65" t="n"/>
       <c r="F28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K28" s="32">
         <f>$D$5</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="29" ht="31.05" customHeight="1" s="71">
@@ -5238,27 +5952,27 @@
       <c r="E29" s="65" t="n"/>
       <c r="F29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K29" s="32">
         <f>$D$8</f>
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" ht="31.05" customHeight="1" s="71">
@@ -5279,27 +5993,27 @@
       <c r="E30" s="65" t="n"/>
       <c r="F30" s="34">
         <f>G11</f>
-        <v>130.32078774617062</v>
+        <v>115.84070021881833</v>
       </c>
       <c r="G30" s="34">
         <f>G12</f>
-        <v>130.32078774617062</v>
+        <v>115.84070021881833</v>
       </c>
       <c r="H30" s="34">
         <f>G13</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="I30" s="34">
         <f>G14</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="J30" s="34">
         <f>G15</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
       <c r="K30" s="34">
         <f>G16</f>
-        <v>112.94468271334797</v>
+        <v>100.39527352297598</v>
       </c>
     </row>
     <row r="31" ht="31.05" customHeight="1" s="71">
@@ -5320,27 +6034,27 @@
       <c r="E31" s="65" t="n"/>
       <c r="F31" s="31">
         <f>N11</f>
-        <v>78.19247264770237</v>
+        <v>63.71238512035008</v>
       </c>
       <c r="G31" s="31">
         <f>N12</f>
-        <v>78.19247264770237</v>
+        <v>63.71238512035008</v>
       </c>
       <c r="H31" s="31">
         <f>N13</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="I31" s="31">
         <f>N14</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="J31" s="31">
         <f>N15</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
       <c r="K31" s="31">
         <f>N16</f>
-        <v>67.76680962800879</v>
+        <v>55.21740043763679</v>
       </c>
     </row>
     <row r="32" ht="31.05" customHeight="1" s="71">
@@ -5361,27 +6075,27 @@
       <c r="E32" s="65" t="n"/>
       <c r="F32" s="31">
         <f>H11</f>
-        <v>32.580196936542656</v>
+        <v>28.96017505470458</v>
       </c>
       <c r="G32" s="31">
         <f>H12</f>
-        <v>32.580196936542656</v>
+        <v>28.96017505470458</v>
       </c>
       <c r="H32" s="31">
         <f>H13</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="I32" s="31">
         <f>H14</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="J32" s="31">
         <f>H15</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
       <c r="K32" s="31">
         <f>H16</f>
-        <v>28.236170678336993</v>
+        <v>25.098818380743996</v>
       </c>
     </row>
     <row r="33" ht="31.05" customHeight="1" s="71">
@@ -5402,27 +6116,27 @@
       <c r="E33" s="65" t="n"/>
       <c r="F33" s="36">
         <f>I11</f>
-        <v>45.61227571115972</v>
+        <v>34.7522100656455</v>
       </c>
       <c r="G33" s="36">
         <f>I12</f>
-        <v>45.61227571115972</v>
+        <v>34.7522100656455</v>
       </c>
       <c r="H33" s="36">
         <f>I13</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="I33" s="36">
         <f>I14</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="J33" s="36">
         <f>I15</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
       <c r="K33" s="36">
         <f>I16</f>
-        <v>39.5306389496718</v>
+        <v>30.118582056892794</v>
       </c>
     </row>
     <row r="34" ht="31.05" customHeight="1" s="71">
@@ -5443,27 +6157,27 @@
       <c r="E34" s="65" t="n"/>
       <c r="F34" s="37">
         <f>J11</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="37">
         <f>J12</f>
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H34" s="37">
         <f>J13</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="I34" s="37">
         <f>J14</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="J34" s="37">
         <f>J15</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="37">
         <f>J16</f>
-        <v>0.35000000000000003</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35" ht="31.05" customHeight="1" s="71">
@@ -5566,27 +6280,27 @@
       <c r="E37" s="65" t="n"/>
       <c r="F37" s="34">
         <f>K11</f>
-        <v>182.44910284463887</v>
+        <v>162.17698030634565</v>
       </c>
       <c r="G37" s="34">
         <f>K12</f>
-        <v>182.44910284463887</v>
+        <v>162.17698030634565</v>
       </c>
       <c r="H37" s="34">
         <f>K13</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="I37" s="34">
         <f>K14</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="J37" s="34">
         <f>K15</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
       <c r="K37" s="34">
         <f>K16</f>
-        <v>158.12255579868716</v>
+        <v>140.55338293216636</v>
       </c>
     </row>
     <row r="38" ht="31.05" customHeight="1" s="71">
@@ -5671,20 +6385,605 @@
         <v>84.33202975929981</v>
       </c>
     </row>
+    <row r="42" ht="26" customHeight="1" s="71">
+      <c r="B42" s="152" t="inlineStr">
+        <is>
+          <t>ДО → ПІСЛЯ · ціна на полиці при поточній закупівлі та при запиті SIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1" s="71">
+      <c r="B43" s="153" t="str">
+        <f>"Бонус мережі "&amp;ROUND('Цена 120 грн — 33 паллет'!D14*100,0)&amp;" % · маржа "&amp;ROUND('Цена 120 грн — 33 паллет'!C14*100,0)&amp;" % · націнка ×"&amp;'Цена 120 грн — 33 паллет'!E14</f>
+        <v>Бонус мережі 25 % · маржа 30 % · націнка ×1.4</v>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1" s="71">
+      <c r="E44" s="154" t="inlineStr">
+        <is>
+          <t>ДО · поточна закупівля SIAS</t>
+        </is>
+      </c>
+      <c r="F44" s="154" t="n"/>
+      <c r="G44" s="154" t="n"/>
+      <c r="H44" s="154" t="n"/>
+      <c r="I44" s="154" t="n"/>
+      <c r="J44" s="154" t="n"/>
+      <c r="K44" s="155" t="inlineStr">
+        <is>
+          <t>ПІСЛЯ · запит SIAS (одна ціна на 6 SKU)</t>
+        </is>
+      </c>
+      <c r="L44" s="155" t="n"/>
+      <c r="M44" s="155" t="n"/>
+      <c r="N44" s="155" t="n"/>
+      <c r="O44" s="155" t="n"/>
+      <c r="P44" s="155" t="n"/>
+      <c r="Q44" s="156" t="inlineStr">
+        <is>
+          <t>ЗМІНА</t>
+        </is>
+      </c>
+      <c r="R44" s="156" t="n"/>
+    </row>
+    <row r="45" ht="42" customHeight="1" s="71">
+      <c r="A45" s="157" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B45" s="157" t="inlineStr">
+        <is>
+          <t>Позиція</t>
+        </is>
+      </c>
+      <c r="C45" s="157" t="inlineStr">
+        <is>
+          <t>Закупівля SIAS: до → після</t>
+        </is>
+      </c>
+      <c r="D45" s="157" t="inlineStr">
+        <is>
+          <t>Вага, г</t>
+        </is>
+      </c>
+      <c r="E45" s="158" t="inlineStr">
+        <is>
+          <t>Закупівля, €/пач.</t>
+        </is>
+      </c>
+      <c r="F45" s="158" t="inlineStr">
+        <is>
+          <t>СС, ₴/пач.</t>
+        </is>
+      </c>
+      <c r="G45" s="158" t="inlineStr">
+        <is>
+          <t>Ціна партнеру, ₴</t>
+        </is>
+      </c>
+      <c r="H45" s="158" t="inlineStr">
+        <is>
+          <t>Бонус мережі, ₴</t>
+        </is>
+      </c>
+      <c r="I45" s="158" t="inlineStr">
+        <is>
+          <t>Залишається після бонусу, ₴</t>
+        </is>
+      </c>
+      <c r="J45" s="158" t="inlineStr">
+        <is>
+          <t>Полиця з ПДВ, ₴</t>
+        </is>
+      </c>
+      <c r="K45" s="159" t="inlineStr">
+        <is>
+          <t>Закупівля, €/пач.</t>
+        </is>
+      </c>
+      <c r="L45" s="159" t="inlineStr">
+        <is>
+          <t>СС, ₴/пач.</t>
+        </is>
+      </c>
+      <c r="M45" s="159" t="inlineStr">
+        <is>
+          <t>Ціна партнеру, ₴</t>
+        </is>
+      </c>
+      <c r="N45" s="159" t="inlineStr">
+        <is>
+          <t>Бонус мережі, ₴</t>
+        </is>
+      </c>
+      <c r="O45" s="159" t="inlineStr">
+        <is>
+          <t>Залишається після бонусу, ₴</t>
+        </is>
+      </c>
+      <c r="P45" s="159" t="inlineStr">
+        <is>
+          <t>Полиця з ПДВ, ₴</t>
+        </is>
+      </c>
+      <c r="Q45" s="160" t="inlineStr">
+        <is>
+          <t>Δ полиці, ₴</t>
+        </is>
+      </c>
+      <c r="R45" s="160" t="inlineStr">
+        <is>
+          <t>Δ полиці, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1" s="71">
+      <c r="A46" s="161">
+        <f>A11</f>
+        <v>1</v>
+      </c>
+      <c r="B46" s="162" t="str">
+        <f>C11</f>
+        <v>Gouda Cheese 123 г</v>
+      </c>
+      <c r="C46" s="161" t="str">
+        <f>"€"&amp;ROUND(E46,2)&amp;" → €"&amp;ROUND(K46,2)</f>
+        <v>€0.75 → €0.54</v>
+      </c>
+      <c r="D46" s="161">
+        <f>D11</f>
+        <v>123</v>
+      </c>
+      <c r="E46" s="163">
+        <f>'Цена 120 грн — 33 паллет'!$B$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="F46" s="164">
+        <f>F11</f>
+        <v>52.12831509846825</v>
+      </c>
+      <c r="G46" s="164">
+        <f>G11</f>
+        <v>115.84070021881833</v>
+      </c>
+      <c r="H46" s="164">
+        <f>H11</f>
+        <v>28.96017505470458</v>
+      </c>
+      <c r="I46" s="164">
+        <f>I11</f>
+        <v>34.7522100656455</v>
+      </c>
+      <c r="J46" s="165">
+        <f>K11</f>
+        <v>162.17698030634565</v>
+      </c>
+      <c r="K46" s="166">
+        <f>'Цена 120 грн — 33 паллет'!$B$19</f>
+        <v>0.54</v>
+      </c>
+      <c r="L46" s="167">
+        <f>'Цена 120 грн — 33 паллет'!$C$8</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="M46" s="167">
+        <f>L46/(1-$D$4-$D$5)</f>
+        <v>85.61661414141415</v>
+      </c>
+      <c r="N46" s="167">
+        <f>M46*$D$4</f>
+        <v>21.404153535353537</v>
+      </c>
+      <c r="O46" s="167">
+        <f>M46-L46-N46</f>
+        <v>25.684984242424242</v>
+      </c>
+      <c r="P46" s="168">
+        <f>M46*$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="Q46" s="169">
+        <f>P46-J46</f>
+        <v>-42.31372050836586</v>
+      </c>
+      <c r="R46" s="170">
+        <f>Q46/J46</f>
+        <v>-0.2609107681524035</v>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1" s="71">
+      <c r="A47" s="161">
+        <f>A12</f>
+        <v>2</v>
+      </c>
+      <c r="B47" s="162" t="str">
+        <f>C12</f>
+        <v>Carbonara Spicy 131 г</v>
+      </c>
+      <c r="C47" s="161" t="str">
+        <f>"€"&amp;ROUND(E47,2)&amp;" → €"&amp;ROUND(K47,2)</f>
+        <v>€0.75 → €0.54</v>
+      </c>
+      <c r="D47" s="161">
+        <f>D12</f>
+        <v>131</v>
+      </c>
+      <c r="E47" s="163">
+        <f>'Цена 120 грн — 33 паллет'!$B$7</f>
+        <v>0.75</v>
+      </c>
+      <c r="F47" s="164">
+        <f>F12</f>
+        <v>52.12831509846825</v>
+      </c>
+      <c r="G47" s="164">
+        <f>G12</f>
+        <v>115.84070021881833</v>
+      </c>
+      <c r="H47" s="164">
+        <f>H12</f>
+        <v>28.96017505470458</v>
+      </c>
+      <c r="I47" s="164">
+        <f>I12</f>
+        <v>34.7522100656455</v>
+      </c>
+      <c r="J47" s="165">
+        <f>K12</f>
+        <v>162.17698030634565</v>
+      </c>
+      <c r="K47" s="166">
+        <f>'Цена 120 грн — 33 паллет'!$B$19</f>
+        <v>0.54</v>
+      </c>
+      <c r="L47" s="167">
+        <f>'Цена 120 грн — 33 паллет'!$C$8</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="M47" s="167">
+        <f>L47/(1-$D$4-$D$5)</f>
+        <v>85.61661414141415</v>
+      </c>
+      <c r="N47" s="167">
+        <f>M47*$D$4</f>
+        <v>21.404153535353537</v>
+      </c>
+      <c r="O47" s="167">
+        <f>M47-L47-N47</f>
+        <v>25.684984242424242</v>
+      </c>
+      <c r="P47" s="168">
+        <f>M47*$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="Q47" s="169">
+        <f>P47-J47</f>
+        <v>-42.31372050836586</v>
+      </c>
+      <c r="R47" s="170">
+        <f>Q47/J47</f>
+        <v>-0.2609107681524035</v>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1" s="71">
+      <c r="A48" s="161">
+        <f>A13</f>
+        <v>3</v>
+      </c>
+      <c r="B48" s="162" t="str">
+        <f>C13</f>
+        <v>Vegetable Flavor 113 г</v>
+      </c>
+      <c r="C48" s="161" t="str">
+        <f>"€"&amp;ROUND(E48,2)&amp;" → €"&amp;ROUND(K48,2)</f>
+        <v>€0.65 → €0.54</v>
+      </c>
+      <c r="D48" s="161">
+        <f>D13</f>
+        <v>113</v>
+      </c>
+      <c r="E48" s="163">
+        <f>'Цена 120 грн — 33 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F48" s="164">
+        <f>F13</f>
+        <v>45.17787308533919</v>
+      </c>
+      <c r="G48" s="164">
+        <f>G13</f>
+        <v>100.39527352297598</v>
+      </c>
+      <c r="H48" s="164">
+        <f>H13</f>
+        <v>25.098818380743996</v>
+      </c>
+      <c r="I48" s="164">
+        <f>I13</f>
+        <v>30.118582056892794</v>
+      </c>
+      <c r="J48" s="165">
+        <f>K13</f>
+        <v>140.55338293216636</v>
+      </c>
+      <c r="K48" s="166">
+        <f>'Цена 120 грн — 33 паллет'!$B$19</f>
+        <v>0.54</v>
+      </c>
+      <c r="L48" s="167">
+        <f>'Цена 120 грн — 33 паллет'!$C$8</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="M48" s="167">
+        <f>L48/(1-$D$4-$D$5)</f>
+        <v>85.61661414141415</v>
+      </c>
+      <c r="N48" s="167">
+        <f>M48*$D$4</f>
+        <v>21.404153535353537</v>
+      </c>
+      <c r="O48" s="167">
+        <f>M48-L48-N48</f>
+        <v>25.684984242424242</v>
+      </c>
+      <c r="P48" s="168">
+        <f>M48*$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="Q48" s="169">
+        <f>P48-J48</f>
+        <v>-20.690123134186564</v>
+      </c>
+      <c r="R48" s="170">
+        <f>Q48/J48</f>
+        <v>-0.14720473248354327</v>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1" s="71">
+      <c r="A49" s="161">
+        <f>A14</f>
+        <v>4</v>
+      </c>
+      <c r="B49" s="162" t="str">
+        <f>C14</f>
+        <v>Spicy Flavor 112.5 г</v>
+      </c>
+      <c r="C49" s="161" t="str">
+        <f>"€"&amp;ROUND(E49,2)&amp;" → €"&amp;ROUND(K49,2)</f>
+        <v>€0.65 → €0.54</v>
+      </c>
+      <c r="D49" s="161">
+        <f>D14</f>
+        <v>112.5</v>
+      </c>
+      <c r="E49" s="163">
+        <f>'Цена 120 грн — 33 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F49" s="164">
+        <f>F14</f>
+        <v>45.17787308533919</v>
+      </c>
+      <c r="G49" s="164">
+        <f>G14</f>
+        <v>100.39527352297598</v>
+      </c>
+      <c r="H49" s="164">
+        <f>H14</f>
+        <v>25.098818380743996</v>
+      </c>
+      <c r="I49" s="164">
+        <f>I14</f>
+        <v>30.118582056892794</v>
+      </c>
+      <c r="J49" s="165">
+        <f>K14</f>
+        <v>140.55338293216636</v>
+      </c>
+      <c r="K49" s="166">
+        <f>'Цена 120 грн — 33 паллет'!$B$19</f>
+        <v>0.54</v>
+      </c>
+      <c r="L49" s="167">
+        <f>'Цена 120 грн — 33 паллет'!$C$8</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="M49" s="167">
+        <f>L49/(1-$D$4-$D$5)</f>
+        <v>85.61661414141415</v>
+      </c>
+      <c r="N49" s="167">
+        <f>M49*$D$4</f>
+        <v>21.404153535353537</v>
+      </c>
+      <c r="O49" s="167">
+        <f>M49-L49-N49</f>
+        <v>25.684984242424242</v>
+      </c>
+      <c r="P49" s="168">
+        <f>M49*$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="Q49" s="169">
+        <f>P49-J49</f>
+        <v>-20.690123134186564</v>
+      </c>
+      <c r="R49" s="170">
+        <f>Q49/J49</f>
+        <v>-0.14720473248354327</v>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1" s="71">
+      <c r="A50" s="161">
+        <f>A15</f>
+        <v>5</v>
+      </c>
+      <c r="B50" s="162" t="str">
+        <f>C15</f>
+        <v>Beef Flavor 113 г</v>
+      </c>
+      <c r="C50" s="161" t="str">
+        <f>"€"&amp;ROUND(E50,2)&amp;" → €"&amp;ROUND(K50,2)</f>
+        <v>€0.65 → €0.54</v>
+      </c>
+      <c r="D50" s="161">
+        <f>D15</f>
+        <v>113</v>
+      </c>
+      <c r="E50" s="163">
+        <f>'Цена 120 грн — 33 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F50" s="164">
+        <f>F15</f>
+        <v>45.17787308533919</v>
+      </c>
+      <c r="G50" s="164">
+        <f>G15</f>
+        <v>100.39527352297598</v>
+      </c>
+      <c r="H50" s="164">
+        <f>H15</f>
+        <v>25.098818380743996</v>
+      </c>
+      <c r="I50" s="164">
+        <f>I15</f>
+        <v>30.118582056892794</v>
+      </c>
+      <c r="J50" s="165">
+        <f>K15</f>
+        <v>140.55338293216636</v>
+      </c>
+      <c r="K50" s="166">
+        <f>'Цена 120 грн — 33 паллет'!$B$19</f>
+        <v>0.54</v>
+      </c>
+      <c r="L50" s="167">
+        <f>'Цена 120 грн — 33 паллет'!$C$8</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="M50" s="167">
+        <f>L50/(1-$D$4-$D$5)</f>
+        <v>85.61661414141415</v>
+      </c>
+      <c r="N50" s="167">
+        <f>M50*$D$4</f>
+        <v>21.404153535353537</v>
+      </c>
+      <c r="O50" s="167">
+        <f>M50-L50-N50</f>
+        <v>25.684984242424242</v>
+      </c>
+      <c r="P50" s="168">
+        <f>M50*$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="Q50" s="169">
+        <f>P50-J50</f>
+        <v>-20.690123134186564</v>
+      </c>
+      <c r="R50" s="170">
+        <f>Q50/J50</f>
+        <v>-0.14720473248354327</v>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1" s="71">
+      <c r="A51" s="161">
+        <f>A16</f>
+        <v>6</v>
+      </c>
+      <c r="B51" s="162" t="str">
+        <f>C16</f>
+        <v>Chicken Flavor 113 г</v>
+      </c>
+      <c r="C51" s="161" t="str">
+        <f>"€"&amp;ROUND(E51,2)&amp;" → €"&amp;ROUND(K51,2)</f>
+        <v>€0.65 → €0.54</v>
+      </c>
+      <c r="D51" s="161">
+        <f>D16</f>
+        <v>113</v>
+      </c>
+      <c r="E51" s="163">
+        <f>'Цена 120 грн — 33 паллет'!$B$5</f>
+        <v>0.65</v>
+      </c>
+      <c r="F51" s="164">
+        <f>F16</f>
+        <v>45.17787308533919</v>
+      </c>
+      <c r="G51" s="164">
+        <f>G16</f>
+        <v>100.39527352297598</v>
+      </c>
+      <c r="H51" s="164">
+        <f>H16</f>
+        <v>25.098818380743996</v>
+      </c>
+      <c r="I51" s="164">
+        <f>I16</f>
+        <v>30.118582056892794</v>
+      </c>
+      <c r="J51" s="165">
+        <f>K16</f>
+        <v>140.55338293216636</v>
+      </c>
+      <c r="K51" s="166">
+        <f>'Цена 120 грн — 33 паллет'!$B$19</f>
+        <v>0.54</v>
+      </c>
+      <c r="L51" s="167">
+        <f>'Цена 120 грн — 33 паллет'!$C$8</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="M51" s="167">
+        <f>L51/(1-$D$4-$D$5)</f>
+        <v>85.61661414141415</v>
+      </c>
+      <c r="N51" s="167">
+        <f>M51*$D$4</f>
+        <v>21.404153535353537</v>
+      </c>
+      <c r="O51" s="167">
+        <f>M51-L51-N51</f>
+        <v>25.684984242424242</v>
+      </c>
+      <c r="P51" s="168">
+        <f>M51*$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="Q51" s="169">
+        <f>P51-J51</f>
+        <v>-20.690123134186564</v>
+      </c>
+      <c r="R51" s="170">
+        <f>Q51/J51</f>
+        <v>-0.14720473248354327</v>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1" s="71">
+      <c r="B53" s="171" t="inlineStr">
+        <is>
+          <t>СС «до» — реальна (Self-Cost), «після» — розрахунок на запит SIAS (логістика рівномірно на пачку). Бонус, маржа та націнка — з аркуша «Цена 120 грн».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="69">
     <mergeCell ref="U9:Y9"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="D34:E34"/>
+    <mergeCell ref="K44:P44"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="E7:K7"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="P9:T9"/>
     <mergeCell ref="D21:E21"/>
@@ -5693,22 +6992,27 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B43:R43"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B42:R42"/>
+    <mergeCell ref="E44:J44"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E5:K5"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B53:R53"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="E4:K4"/>
     <mergeCell ref="D28:E28"/>
+    <mergeCell ref="Q44:R44"/>
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="AE9:AI9"/>
     <mergeCell ref="D39:E39"/>
@@ -5744,7 +7048,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AI59" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:AI73" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5756,7 +7060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38" customWidth="1" style="71" min="1" max="1"/>
@@ -6232,7 +7536,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I42" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:H42" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6244,7 +7548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38" customWidth="1" style="71" min="1" max="1"/>
@@ -6718,7 +8022,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I41" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:H41" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/RAMEN_FINMODEL_REAL_UA.xlsx
+++ b/RAMEN_FINMODEL_REAL_UA.xlsx
@@ -34,14 +34,14 @@
     <numFmt numFmtId="176" formatCode="&quot;€&quot;0.000"/>
     <numFmt numFmtId="177" formatCode="\+#,##0.00&quot; ₴&quot;;\-#,##0.00&quot; ₴&quot;"/>
     <numFmt numFmtId="178" formatCode="\+&quot;€&quot;0.000;\-&quot;€&quot;0.000"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
-    <numFmt numFmtId="183" formatCode="+#,##0.00&quot; ₴&quot;;-#,##0.00&quot; ₴&quot;"/>
-    <numFmt numFmtId="184" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="179" formatCode="+#,##0.00&quot; ₴&quot;;-#,##0.00&quot; ₴&quot;"/>
+    <numFmt numFmtId="180" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="181" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="182" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
+    <numFmt numFmtId="183" formatCode="_(\$* #,##0.00_);_(\$* \(#,##0.00\);_(\$* \-??_);_(@_)"/>
+    <numFmt numFmtId="184" formatCode="_(\$* #,##0_);_(\$* \(#,##0\);_(\$* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -275,6 +275,23 @@
       <color rgb="FFA33A3A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFA33A3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF222222"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF203864"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="32">
     <fill>
@@ -432,7 +449,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -779,17 +796,61 @@
         <color rgb="00C9D3E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D3E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D3E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C9D3E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C9D3E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="11" fillId="19" borderId="10"/>
-    <xf numFmtId="179" fontId="1" fillId="19" borderId="10"/>
-    <xf numFmtId="180" fontId="1" fillId="19" borderId="10"/>
     <xf numFmtId="181" fontId="1" fillId="19" borderId="10"/>
     <xf numFmtId="182" fontId="1" fillId="19" borderId="10"/>
+    <xf numFmtId="183" fontId="1" fillId="19" borderId="10"/>
+    <xf numFmtId="184" fontId="1" fillId="19" borderId="10"/>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="10"/>
     <xf numFmtId="9" fontId="1" fillId="19" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1257,14 +1318,46 @@
     <xf numFmtId="171" fontId="5" fillId="21" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="183" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="179" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="40" fillId="31" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="23" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="42" fillId="23" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="43" fillId="21" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="14" fillId="30" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="30" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1553,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI53"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="71" min="1" max="1"/>
@@ -3651,27 +3744,27 @@
           <t>ДО · поточна закупівля SIAS</t>
         </is>
       </c>
-      <c r="F44" s="154" t="n"/>
-      <c r="G44" s="154" t="n"/>
-      <c r="H44" s="154" t="n"/>
-      <c r="I44" s="154" t="n"/>
-      <c r="J44" s="154" t="n"/>
+      <c r="F44" s="172" t="n"/>
+      <c r="G44" s="172" t="n"/>
+      <c r="H44" s="172" t="n"/>
+      <c r="I44" s="172" t="n"/>
+      <c r="J44" s="173" t="n"/>
       <c r="K44" s="155" t="inlineStr">
         <is>
           <t>ПІСЛЯ · запит SIAS (одна ціна на 6 SKU)</t>
         </is>
       </c>
-      <c r="L44" s="155" t="n"/>
-      <c r="M44" s="155" t="n"/>
-      <c r="N44" s="155" t="n"/>
-      <c r="O44" s="155" t="n"/>
-      <c r="P44" s="155" t="n"/>
+      <c r="L44" s="172" t="n"/>
+      <c r="M44" s="172" t="n"/>
+      <c r="N44" s="172" t="n"/>
+      <c r="O44" s="172" t="n"/>
+      <c r="P44" s="173" t="n"/>
       <c r="Q44" s="156" t="inlineStr">
         <is>
           <t>ЗМІНА</t>
         </is>
       </c>
-      <c r="R44" s="156" t="n"/>
+      <c r="R44" s="173" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1" s="71">
       <c r="A45" s="157" t="inlineStr">
@@ -3830,11 +3923,11 @@
         <f>M46*$D$6</f>
         <v>118.71850666666664</v>
       </c>
-      <c r="Q46" s="169">
+      <c r="Q46" s="174">
         <f>P46-J46</f>
         <v>-89.71349333333337</v>
       </c>
-      <c r="R46" s="170">
+      <c r="R46" s="175">
         <f>Q46/J46</f>
         <v>-0.4304209206519794</v>
       </c>
@@ -3904,11 +3997,11 @@
         <f>M47*$D$6</f>
         <v>118.71850666666664</v>
       </c>
-      <c r="Q47" s="169">
+      <c r="Q47" s="174">
         <f>P47-J47</f>
         <v>-89.71349333333337</v>
       </c>
-      <c r="R47" s="170">
+      <c r="R47" s="175">
         <f>Q47/J47</f>
         <v>-0.4304209206519794</v>
       </c>
@@ -3978,11 +4071,11 @@
         <f>M48*$D$6</f>
         <v>118.71850666666664</v>
       </c>
-      <c r="Q48" s="169">
+      <c r="Q48" s="174">
         <f>P48-J48</f>
         <v>-61.92255999999999</v>
       </c>
-      <c r="R48" s="170">
+      <c r="R48" s="175">
         <f>Q48/J48</f>
         <v>-0.342793369983053</v>
       </c>
@@ -4052,11 +4145,11 @@
         <f>M49*$D$6</f>
         <v>118.71850666666664</v>
       </c>
-      <c r="Q49" s="169">
+      <c r="Q49" s="174">
         <f>P49-J49</f>
         <v>-61.92255999999999</v>
       </c>
-      <c r="R49" s="170">
+      <c r="R49" s="175">
         <f>Q49/J49</f>
         <v>-0.342793369983053</v>
       </c>
@@ -4126,11 +4219,11 @@
         <f>M50*$D$6</f>
         <v>118.71850666666664</v>
       </c>
-      <c r="Q50" s="169">
+      <c r="Q50" s="174">
         <f>P50-J50</f>
         <v>-61.92255999999999</v>
       </c>
-      <c r="R50" s="170">
+      <c r="R50" s="175">
         <f>Q50/J50</f>
         <v>-0.342793369983053</v>
       </c>
@@ -4200,11 +4293,11 @@
         <f>M51*$D$6</f>
         <v>118.71850666666664</v>
       </c>
-      <c r="Q51" s="169">
+      <c r="Q51" s="174">
         <f>P51-J51</f>
         <v>-61.92255999999999</v>
       </c>
-      <c r="R51" s="170">
+      <c r="R51" s="175">
         <f>Q51/J51</f>
         <v>-0.342793369983053</v>
       </c>
@@ -4216,8 +4309,397 @@
         </is>
       </c>
     </row>
+    <row r="56" ht="26" customHeight="1" s="71">
+      <c r="B56" s="152" t="inlineStr">
+        <is>
+          <t>СЦЕНАРІЇ МАРЖІ · ДО та ПІСЛЯ запиту SIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1" s="71">
+      <c r="B57" s="54" t="inlineStr">
+        <is>
+          <t>Для кожної маржі: полиця при поточній закупівлі (ДО) і закупівля, яку має прийняти SIAS, щоб полиця була 120 ₴ (ПІСЛЯ). Бонус мережі та націнка — як на аркуші «Цена 120 грн».</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1" s="71">
+      <c r="E58" s="154" t="inlineStr">
+        <is>
+          <t>ДО · поточна закупівля</t>
+        </is>
+      </c>
+      <c r="F58" s="154" t="n"/>
+      <c r="G58" s="155" t="inlineStr">
+        <is>
+          <t>ПІСЛЯ · запит для полиці 120 ₴</t>
+        </is>
+      </c>
+      <c r="H58" s="155" t="n"/>
+      <c r="I58" s="155" t="n"/>
+      <c r="J58" s="156" t="inlineStr">
+        <is>
+          <t>ЗМІНА відносно ДО</t>
+        </is>
+      </c>
+      <c r="K58" s="156" t="n"/>
+      <c r="L58" s="156" t="n"/>
+      <c r="M58" s="156" t="n"/>
+    </row>
+    <row r="59" ht="38" customHeight="1" s="71">
+      <c r="B59" s="157" t="inlineStr">
+        <is>
+          <t>Маржа</t>
+        </is>
+      </c>
+      <c r="C59" s="157" t="inlineStr"/>
+      <c r="D59" s="157" t="inlineStr">
+        <is>
+          <t>Частка ціни на СС</t>
+        </is>
+      </c>
+      <c r="E59" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="F59" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="G59" s="159" t="inlineStr">
+        <is>
+          <t>Запит, €/пач.</t>
+        </is>
+      </c>
+      <c r="H59" s="159" t="inlineStr">
+        <is>
+          <t>СС, ₴</t>
+        </is>
+      </c>
+      <c r="I59" s="159" t="inlineStr">
+        <is>
+          <t>Полиця, ₴</t>
+        </is>
+      </c>
+      <c r="J59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="K59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, %</t>
+        </is>
+      </c>
+      <c r="L59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="M59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1" s="71">
+      <c r="B60" s="176" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C60" s="177" t="str">
+        <f>IF(ABS(B60-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D60" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-B60</f>
+        <v>0.4</v>
+      </c>
+      <c r="E60" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/D60*'Финмодель 6 паллет'!$D$6</f>
+        <v>203.22119999999998</v>
+      </c>
+      <c r="F60" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/D60*'Финмодель 6 паллет'!$D$6</f>
+        <v>234.486</v>
+      </c>
+      <c r="G60" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*D60/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="H60" s="182">
+        <f>(G60*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(G60+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(G60+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>33.751200000000004</v>
+      </c>
+      <c r="I60" s="183">
+        <f>H60/D60*'Финмодель 6 паллет'!$D$6</f>
+        <v>118.1292</v>
+      </c>
+      <c r="J60" s="174">
+        <f>I60-E60</f>
+        <v>-85.09199999999998</v>
+      </c>
+      <c r="K60" s="175">
+        <f>J60/E60</f>
+        <v>-0.41871615756623815</v>
+      </c>
+      <c r="L60" s="174">
+        <f>I60-F60</f>
+        <v>-116.35679999999999</v>
+      </c>
+      <c r="M60" s="175">
+        <f>L60/F60</f>
+        <v>-0.49622066989073976</v>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1" s="71">
+      <c r="B61" s="176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C61" s="177" t="str">
+        <f>IF(ABS(B61-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v>◄ поточна</v>
+      </c>
+      <c r="D61" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-B61</f>
+        <v>0.45</v>
+      </c>
+      <c r="E61" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/D61*'Финмодель 6 паллет'!$D$6</f>
+        <v>180.64106666666663</v>
+      </c>
+      <c r="F61" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/D61*'Финмодель 6 паллет'!$D$6</f>
+        <v>208.43200000000002</v>
+      </c>
+      <c r="G61" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*D61/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.32</v>
+      </c>
+      <c r="H61" s="182">
+        <f>(G61*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(G61+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(G61+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="I61" s="183">
+        <f>H61/D61*'Финмодель 6 паллет'!$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="J61" s="174">
+        <f>I61-E61</f>
+        <v>-61.92255999999999</v>
+      </c>
+      <c r="K61" s="175">
+        <f>J61/E61</f>
+        <v>-0.342793369983053</v>
+      </c>
+      <c r="L61" s="174">
+        <f>I61-F61</f>
+        <v>-89.71349333333337</v>
+      </c>
+      <c r="M61" s="175">
+        <f>L61/F61</f>
+        <v>-0.4304209206519794</v>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1" s="71">
+      <c r="B62" s="176" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C62" s="177" t="str">
+        <f>IF(ABS(B62-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D62" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-B62</f>
+        <v>0.5</v>
+      </c>
+      <c r="E62" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/D62*'Финмодель 6 паллет'!$D$6</f>
+        <v>162.57695999999999</v>
+      </c>
+      <c r="F62" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/D62*'Финмодель 6 паллет'!$D$6</f>
+        <v>187.58880000000002</v>
+      </c>
+      <c r="G62" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*D62/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="H62" s="182">
+        <f>(G62*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(G62+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(G62+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>42.56784</v>
+      </c>
+      <c r="I62" s="183">
+        <f>H62/D62*'Финмодель 6 паллет'!$D$6</f>
+        <v>119.18995199999998</v>
+      </c>
+      <c r="J62" s="174">
+        <f>I62-E62</f>
+        <v>-43.38700800000001</v>
+      </c>
+      <c r="K62" s="175">
+        <f>J62/E62</f>
+        <v>-0.26687058239986783</v>
+      </c>
+      <c r="L62" s="174">
+        <f>I62-F62</f>
+        <v>-68.39884800000004</v>
+      </c>
+      <c r="M62" s="175">
+        <f>L62/F62</f>
+        <v>-0.36462117141321887</v>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1" s="71">
+      <c r="B63" s="176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C63" s="177" t="str">
+        <f>IF(ABS(B63-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D63" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-B63</f>
+        <v>0.55</v>
+      </c>
+      <c r="E63" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/D63*'Финмодель 6 паллет'!$D$6</f>
+        <v>147.79723636363633</v>
+      </c>
+      <c r="F63" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/D63*'Финмодель 6 паллет'!$D$6</f>
+        <v>170.5352727272727</v>
+      </c>
+      <c r="G63" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*D63/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="H63" s="182">
+        <f>(G63*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(G63+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(G63+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>46.97616</v>
+      </c>
+      <c r="I63" s="183">
+        <f>H63/D63*'Финмодель 6 паллет'!$D$6</f>
+        <v>119.57567999999998</v>
+      </c>
+      <c r="J63" s="174">
+        <f>I63-E63</f>
+        <v>-28.221556363636353</v>
+      </c>
+      <c r="K63" s="175">
+        <f>J63/E63</f>
+        <v>-0.19094779481668248</v>
+      </c>
+      <c r="L63" s="174">
+        <f>I63-F63</f>
+        <v>-50.959592727272735</v>
+      </c>
+      <c r="M63" s="175">
+        <f>L63/F63</f>
+        <v>-0.29882142217445823</v>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1" s="71">
+      <c r="B64" s="176" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C64" s="177" t="str">
+        <f>IF(ABS(B64-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D64" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-B64</f>
+        <v>0.6</v>
+      </c>
+      <c r="E64" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/D64*'Финмодель 6 паллет'!$D$6</f>
+        <v>135.4808</v>
+      </c>
+      <c r="F64" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/D64*'Финмодель 6 паллет'!$D$6</f>
+        <v>156.324</v>
+      </c>
+      <c r="G64" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*D64/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.53</v>
+      </c>
+      <c r="H64" s="182">
+        <f>(G64*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(G64+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(G64+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>51.38448</v>
+      </c>
+      <c r="I64" s="183">
+        <f>H64/D64*'Финмодель 6 паллет'!$D$6</f>
+        <v>119.89712000000002</v>
+      </c>
+      <c r="J64" s="174">
+        <f>I64-E64</f>
+        <v>-15.583679999999973</v>
+      </c>
+      <c r="K64" s="175">
+        <f>J64/E64</f>
+        <v>-0.1150250072334971</v>
+      </c>
+      <c r="L64" s="174">
+        <f>I64-F64</f>
+        <v>-36.42688</v>
+      </c>
+      <c r="M64" s="175">
+        <f>L64/F64</f>
+        <v>-0.23302167293569762</v>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1" s="71">
+      <c r="B65" s="176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C65" s="177" t="str">
+        <f>IF(ABS(B65-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D65" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-B65</f>
+        <v>0.65</v>
+      </c>
+      <c r="E65" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/D65*'Финмодель 6 паллет'!$D$6</f>
+        <v>125.05919999999998</v>
+      </c>
+      <c r="F65" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/D65*'Финмодель 6 паллет'!$D$6</f>
+        <v>144.29907692307694</v>
+      </c>
+      <c r="G65" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*D65/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="H65" s="182">
+        <f>(G65*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(G65+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(G65+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>55.163039999999995</v>
+      </c>
+      <c r="I65" s="183">
+        <f>H65/D65*'Финмодель 6 паллет'!$D$6</f>
+        <v>118.81270153846151</v>
+      </c>
+      <c r="J65" s="174">
+        <f>I65-E65</f>
+        <v>-6.246498461538465</v>
+      </c>
+      <c r="K65" s="175">
+        <f>J65/E65</f>
+        <v>-0.04994833216219571</v>
+      </c>
+      <c r="L65" s="174">
+        <f>I65-F65</f>
+        <v>-25.486375384615428</v>
+      </c>
+      <c r="M65" s="175">
+        <f>L65/F65</f>
+        <v>-0.1766218878739032</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="74">
     <mergeCell ref="U9:Y9"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
@@ -4227,6 +4709,7 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B57:M57"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D36:E36"/>
@@ -4239,6 +4722,8 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="J58:M58"/>
     <mergeCell ref="B43:R43"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="D27:E27"/>
@@ -4253,6 +4738,7 @@
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B53:R53"/>
+    <mergeCell ref="E58:F58"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
@@ -4281,6 +4767,7 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="E6:K6"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B56:M56"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="Z9:AD9"/>
     <mergeCell ref="D26:E26"/>
@@ -4295,7 +4782,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AI73" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:AI85" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4306,7 +4793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI53"/>
+  <dimension ref="A1:AI65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="4" customWidth="1" style="71" min="1" max="1"/>
@@ -6404,27 +6891,27 @@
           <t>ДО · поточна закупівля SIAS</t>
         </is>
       </c>
-      <c r="F44" s="154" t="n"/>
-      <c r="G44" s="154" t="n"/>
-      <c r="H44" s="154" t="n"/>
-      <c r="I44" s="154" t="n"/>
-      <c r="J44" s="154" t="n"/>
+      <c r="F44" s="172" t="n"/>
+      <c r="G44" s="172" t="n"/>
+      <c r="H44" s="172" t="n"/>
+      <c r="I44" s="172" t="n"/>
+      <c r="J44" s="173" t="n"/>
       <c r="K44" s="155" t="inlineStr">
         <is>
           <t>ПІСЛЯ · запит SIAS (одна ціна на 6 SKU)</t>
         </is>
       </c>
-      <c r="L44" s="155" t="n"/>
-      <c r="M44" s="155" t="n"/>
-      <c r="N44" s="155" t="n"/>
-      <c r="O44" s="155" t="n"/>
-      <c r="P44" s="155" t="n"/>
+      <c r="L44" s="172" t="n"/>
+      <c r="M44" s="172" t="n"/>
+      <c r="N44" s="172" t="n"/>
+      <c r="O44" s="172" t="n"/>
+      <c r="P44" s="173" t="n"/>
       <c r="Q44" s="156" t="inlineStr">
         <is>
           <t>ЗМІНА</t>
         </is>
       </c>
-      <c r="R44" s="156" t="n"/>
+      <c r="R44" s="173" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1" s="71">
       <c r="A45" s="157" t="inlineStr">
@@ -6583,11 +7070,11 @@
         <f>M46*$D$6</f>
         <v>119.8632597979798</v>
       </c>
-      <c r="Q46" s="169">
+      <c r="Q46" s="174">
         <f>P46-J46</f>
         <v>-42.31372050836586</v>
       </c>
-      <c r="R46" s="170">
+      <c r="R46" s="175">
         <f>Q46/J46</f>
         <v>-0.2609107681524035</v>
       </c>
@@ -6657,11 +7144,11 @@
         <f>M47*$D$6</f>
         <v>119.8632597979798</v>
       </c>
-      <c r="Q47" s="169">
+      <c r="Q47" s="174">
         <f>P47-J47</f>
         <v>-42.31372050836586</v>
       </c>
-      <c r="R47" s="170">
+      <c r="R47" s="175">
         <f>Q47/J47</f>
         <v>-0.2609107681524035</v>
       </c>
@@ -6731,11 +7218,11 @@
         <f>M48*$D$6</f>
         <v>119.8632597979798</v>
       </c>
-      <c r="Q48" s="169">
+      <c r="Q48" s="174">
         <f>P48-J48</f>
         <v>-20.690123134186564</v>
       </c>
-      <c r="R48" s="170">
+      <c r="R48" s="175">
         <f>Q48/J48</f>
         <v>-0.14720473248354327</v>
       </c>
@@ -6805,11 +7292,11 @@
         <f>M49*$D$6</f>
         <v>119.8632597979798</v>
       </c>
-      <c r="Q49" s="169">
+      <c r="Q49" s="174">
         <f>P49-J49</f>
         <v>-20.690123134186564</v>
       </c>
-      <c r="R49" s="170">
+      <c r="R49" s="175">
         <f>Q49/J49</f>
         <v>-0.14720473248354327</v>
       </c>
@@ -6879,11 +7366,11 @@
         <f>M50*$D$6</f>
         <v>119.8632597979798</v>
       </c>
-      <c r="Q50" s="169">
+      <c r="Q50" s="174">
         <f>P50-J50</f>
         <v>-20.690123134186564</v>
       </c>
-      <c r="R50" s="170">
+      <c r="R50" s="175">
         <f>Q50/J50</f>
         <v>-0.14720473248354327</v>
       </c>
@@ -6953,11 +7440,11 @@
         <f>M51*$D$6</f>
         <v>119.8632597979798</v>
       </c>
-      <c r="Q51" s="169">
+      <c r="Q51" s="174">
         <f>P51-J51</f>
         <v>-20.690123134186564</v>
       </c>
-      <c r="R51" s="170">
+      <c r="R51" s="175">
         <f>Q51/J51</f>
         <v>-0.14720473248354327</v>
       </c>
@@ -6969,8 +7456,397 @@
         </is>
       </c>
     </row>
+    <row r="56" ht="26" customHeight="1" s="71">
+      <c r="B56" s="152" t="inlineStr">
+        <is>
+          <t>СЦЕНАРІЇ МАРЖІ · ДО та ПІСЛЯ запиту SIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1" s="71">
+      <c r="B57" s="54" t="inlineStr">
+        <is>
+          <t>Для кожної маржі: полиця при поточній закупівлі (ДО) і закупівля, яку має прийняти SIAS, щоб полиця була 120 ₴ (ПІСЛЯ). Бонус мережі та націнка — як на аркуші «Цена 120 грн».</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1" s="71">
+      <c r="E58" s="154" t="inlineStr">
+        <is>
+          <t>ДО · поточна закупівля</t>
+        </is>
+      </c>
+      <c r="F58" s="154" t="n"/>
+      <c r="G58" s="155" t="inlineStr">
+        <is>
+          <t>ПІСЛЯ · запит для полиці 120 ₴</t>
+        </is>
+      </c>
+      <c r="H58" s="155" t="n"/>
+      <c r="I58" s="155" t="n"/>
+      <c r="J58" s="156" t="inlineStr">
+        <is>
+          <t>ЗМІНА відносно ДО</t>
+        </is>
+      </c>
+      <c r="K58" s="156" t="n"/>
+      <c r="L58" s="156" t="n"/>
+      <c r="M58" s="156" t="n"/>
+    </row>
+    <row r="59" ht="38" customHeight="1" s="71">
+      <c r="B59" s="157" t="inlineStr">
+        <is>
+          <t>Маржа</t>
+        </is>
+      </c>
+      <c r="C59" s="157" t="inlineStr"/>
+      <c r="D59" s="157" t="inlineStr">
+        <is>
+          <t>Частка ціни на СС</t>
+        </is>
+      </c>
+      <c r="E59" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="F59" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="G59" s="159" t="inlineStr">
+        <is>
+          <t>Запит, €/пач.</t>
+        </is>
+      </c>
+      <c r="H59" s="159" t="inlineStr">
+        <is>
+          <t>СС, ₴</t>
+        </is>
+      </c>
+      <c r="I59" s="159" t="inlineStr">
+        <is>
+          <t>Полиця, ₴</t>
+        </is>
+      </c>
+      <c r="J59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="K59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, %</t>
+        </is>
+      </c>
+      <c r="L59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="M59" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1" s="71">
+      <c r="B60" s="176" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C60" s="177" t="str">
+        <f>IF(ABS(B60-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D60" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-B60</f>
+        <v>0.4</v>
+      </c>
+      <c r="E60" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/D60*'Финмодель 33 паллет'!$D$6</f>
+        <v>158.12255579868716</v>
+      </c>
+      <c r="F60" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/D60*'Финмодель 33 паллет'!$D$6</f>
+        <v>182.44910284463887</v>
+      </c>
+      <c r="G60" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*D60/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="H60" s="182">
+        <f>(G60*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(G60+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(G60+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>34.11915636363636</v>
+      </c>
+      <c r="I60" s="183">
+        <f>H60/D60*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.41704727272723</v>
+      </c>
+      <c r="J60" s="174">
+        <f>I60-E60</f>
+        <v>-38.70550852595993</v>
+      </c>
+      <c r="K60" s="175">
+        <f>J60/E60</f>
+        <v>-0.24478170322036552</v>
+      </c>
+      <c r="L60" s="174">
+        <f>I60-F60</f>
+        <v>-63.03205557191164</v>
+      </c>
+      <c r="M60" s="175">
+        <f>L60/F60</f>
+        <v>-0.34547747612431623</v>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1" s="71">
+      <c r="B61" s="176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C61" s="177" t="str">
+        <f>IF(ABS(B61-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v>◄ поточна</v>
+      </c>
+      <c r="D61" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-B61</f>
+        <v>0.45</v>
+      </c>
+      <c r="E61" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/D61*'Финмодель 33 паллет'!$D$6</f>
+        <v>140.55338293216636</v>
+      </c>
+      <c r="F61" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/D61*'Финмодель 33 паллет'!$D$6</f>
+        <v>162.17698030634565</v>
+      </c>
+      <c r="G61" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*D61/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.54</v>
+      </c>
+      <c r="H61" s="182">
+        <f>(G61*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(G61+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(G61+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="I61" s="183">
+        <f>H61/D61*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="J61" s="174">
+        <f>I61-E61</f>
+        <v>-20.690123134186564</v>
+      </c>
+      <c r="K61" s="175">
+        <f>J61/E61</f>
+        <v>-0.14720473248354327</v>
+      </c>
+      <c r="L61" s="174">
+        <f>I61-F61</f>
+        <v>-42.31372050836586</v>
+      </c>
+      <c r="M61" s="175">
+        <f>L61/F61</f>
+        <v>-0.2609107681524035</v>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1" s="71">
+      <c r="B62" s="176" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C62" s="177" t="str">
+        <f>IF(ABS(B62-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D62" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-B62</f>
+        <v>0.5</v>
+      </c>
+      <c r="E62" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/D62*'Финмодель 33 паллет'!$D$6</f>
+        <v>126.49804463894974</v>
+      </c>
+      <c r="F62" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/D62*'Финмодель 33 паллет'!$D$6</f>
+        <v>145.95928227571108</v>
+      </c>
+      <c r="G62" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*D62/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.6</v>
+      </c>
+      <c r="H62" s="182">
+        <f>(G62*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(G62+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(G62+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>42.30603636363636</v>
+      </c>
+      <c r="I62" s="183">
+        <f>H62/D62*'Финмодель 33 паллет'!$D$6</f>
+        <v>118.45690181818179</v>
+      </c>
+      <c r="J62" s="174">
+        <f>I62-E62</f>
+        <v>-8.041142820767945</v>
+      </c>
+      <c r="K62" s="175">
+        <f>J62/E62</f>
+        <v>-0.06356732899483898</v>
+      </c>
+      <c r="L62" s="174">
+        <f>I62-F62</f>
+        <v>-27.502380457529284</v>
+      </c>
+      <c r="M62" s="175">
+        <f>L62/F62</f>
+        <v>-0.1884250184621929</v>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1" s="71">
+      <c r="B63" s="176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C63" s="177" t="str">
+        <f>IF(ABS(B63-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D63" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-B63</f>
+        <v>0.55</v>
+      </c>
+      <c r="E63" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/D63*'Финмодель 33 паллет'!$D$6</f>
+        <v>114.9982223990452</v>
+      </c>
+      <c r="F63" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/D63*'Финмодель 33 паллет'!$D$6</f>
+        <v>132.6902566142828</v>
+      </c>
+      <c r="G63" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*D63/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.67</v>
+      </c>
+      <c r="H63" s="182">
+        <f>(G63*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(G63+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(G63+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>46.71435636363636</v>
+      </c>
+      <c r="I63" s="183">
+        <f>H63/D63*'Финмодель 33 паллет'!$D$6</f>
+        <v>118.90927074380163</v>
+      </c>
+      <c r="J63" s="174">
+        <f>I63-E63</f>
+        <v>3.9110483447564235</v>
+      </c>
+      <c r="K63" s="175">
+        <f>J63/E63</f>
+        <v>0.0340096417419831</v>
+      </c>
+      <c r="L63" s="174">
+        <f>I63-F63</f>
+        <v>-13.78098587048116</v>
+      </c>
+      <c r="M63" s="175">
+        <f>L63/F63</f>
+        <v>-0.10385831049028037</v>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1" s="71">
+      <c r="B64" s="176" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C64" s="177" t="str">
+        <f>IF(ABS(B64-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D64" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-B64</f>
+        <v>0.6</v>
+      </c>
+      <c r="E64" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/D64*'Финмодель 33 паллет'!$D$6</f>
+        <v>105.41503719912478</v>
+      </c>
+      <c r="F64" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/D64*'Финмодель 33 паллет'!$D$6</f>
+        <v>121.63273522975923</v>
+      </c>
+      <c r="G64" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*D64/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.74</v>
+      </c>
+      <c r="H64" s="182">
+        <f>(G64*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(G64+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(G64+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>51.12267636363635</v>
+      </c>
+      <c r="I64" s="183">
+        <f>H64/D64*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.28624484848483</v>
+      </c>
+      <c r="J64" s="174">
+        <f>I64-E64</f>
+        <v>13.871207649360045</v>
+      </c>
+      <c r="K64" s="175">
+        <f>J64/E64</f>
+        <v>0.131586612478805</v>
+      </c>
+      <c r="L64" s="174">
+        <f>I64-F64</f>
+        <v>-2.346490381274407</v>
+      </c>
+      <c r="M64" s="175">
+        <f>L64/F64</f>
+        <v>-0.019291602518367965</v>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1" s="71">
+      <c r="B65" s="176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C65" s="177" t="str">
+        <f>IF(ABS(B65-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="D65" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-B65</f>
+        <v>0.65</v>
+      </c>
+      <c r="E65" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/D65*'Финмодель 33 паллет'!$D$6</f>
+        <v>97.30618818380749</v>
+      </c>
+      <c r="F65" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/D65*'Финмодель 33 паллет'!$D$6</f>
+        <v>112.27637098131622</v>
+      </c>
+      <c r="G65" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*D65/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.81</v>
+      </c>
+      <c r="H65" s="182">
+        <f>(G65*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(G65+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(G65+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>55.53099636363637</v>
+      </c>
+      <c r="I65" s="183">
+        <f>H65/D65*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.60522293706295</v>
+      </c>
+      <c r="J65" s="174">
+        <f>I65-E65</f>
+        <v>22.299034753255455</v>
+      </c>
+      <c r="K65" s="175">
+        <f>J65/E65</f>
+        <v>0.22916358321562727</v>
+      </c>
+      <c r="L65" s="174">
+        <f>I65-F65</f>
+        <v>7.328851955746728</v>
+      </c>
+      <c r="M65" s="175">
+        <f>L65/F65</f>
+        <v>0.06527510545354476</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="74">
     <mergeCell ref="U9:Y9"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
@@ -6980,6 +7856,7 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B57:M57"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="D36:E36"/>
@@ -6992,6 +7869,8 @@
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G58:I58"/>
+    <mergeCell ref="J58:M58"/>
     <mergeCell ref="B43:R43"/>
     <mergeCell ref="E3:K3"/>
     <mergeCell ref="D27:E27"/>
@@ -7006,6 +7885,7 @@
     <mergeCell ref="E8:K8"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B53:R53"/>
+    <mergeCell ref="E58:F58"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
@@ -7034,6 +7914,7 @@
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="E6:K6"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B56:M56"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="Z9:AD9"/>
     <mergeCell ref="D26:E26"/>
@@ -7048,7 +7929,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AI73" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:AI85" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7060,14 +7941,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38" customWidth="1" style="71" min="1" max="1"/>
     <col width="17" customWidth="1" style="71" min="2" max="2"/>
     <col width="23.88671875" customWidth="1" style="71" min="3" max="3"/>
     <col width="17" customWidth="1" style="71" min="4" max="8"/>
-    <col width="2" customWidth="1" style="71" min="9" max="9"/>
+    <col width="14" customWidth="1" style="71" min="9" max="9"/>
+    <col width="14" customWidth="1" style="71" min="10" max="10"/>
+    <col width="14" customWidth="1" style="71" min="11" max="11"/>
+    <col width="14" customWidth="1" style="71" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7521,14 +8405,408 @@
         <v>38.15951999999999</v>
       </c>
     </row>
+    <row r="28" ht="26" customHeight="1" s="71">
+      <c r="A28" s="152" t="inlineStr">
+        <is>
+          <t>СЦЕНАРІЇ МАРЖІ · ДО та ПІСЛЯ запиту SIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="71">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>Для кожної маржі: полиця при поточній закупівлі (ДО) і закупівля, яку має прийняти SIAS, щоб полиця була 120 ₴ (ПІСЛЯ). Бонус мережі та націнка — як на аркуші «Цена 120 грн».</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" s="71">
+      <c r="D30" s="154" t="inlineStr">
+        <is>
+          <t>ДО · поточна закупівля</t>
+        </is>
+      </c>
+      <c r="E30" s="154" t="n"/>
+      <c r="F30" s="155" t="inlineStr">
+        <is>
+          <t>ПІСЛЯ · запит для полиці 120 ₴</t>
+        </is>
+      </c>
+      <c r="G30" s="155" t="n"/>
+      <c r="H30" s="155" t="n"/>
+      <c r="I30" s="156" t="inlineStr">
+        <is>
+          <t>ЗМІНА відносно ДО</t>
+        </is>
+      </c>
+      <c r="J30" s="156" t="n"/>
+      <c r="K30" s="156" t="n"/>
+      <c r="L30" s="156" t="n"/>
+    </row>
+    <row r="31" ht="38" customHeight="1" s="71">
+      <c r="A31" s="157" t="inlineStr">
+        <is>
+          <t>Маржа</t>
+        </is>
+      </c>
+      <c r="B31" s="157" t="inlineStr"/>
+      <c r="C31" s="157" t="inlineStr">
+        <is>
+          <t>Частка ціни на СС</t>
+        </is>
+      </c>
+      <c r="D31" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="E31" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="F31" s="159" t="inlineStr">
+        <is>
+          <t>Запит, €/пач.</t>
+        </is>
+      </c>
+      <c r="G31" s="159" t="inlineStr">
+        <is>
+          <t>СС, ₴</t>
+        </is>
+      </c>
+      <c r="H31" s="159" t="inlineStr">
+        <is>
+          <t>Полиця, ₴</t>
+        </is>
+      </c>
+      <c r="I31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="J31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, %</t>
+        </is>
+      </c>
+      <c r="K31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="L31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="71">
+      <c r="A32" s="176" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B32" s="177" t="str">
+        <f>IF(ABS(A32-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C32" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-A32</f>
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/C32*'Финмодель 6 паллет'!$D$6</f>
+        <v>203.22119999999998</v>
+      </c>
+      <c r="E32" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/C32*'Финмодель 6 паллет'!$D$6</f>
+        <v>234.486</v>
+      </c>
+      <c r="F32" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*C32/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="G32" s="182">
+        <f>(F32*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(F32+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(F32+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>33.751200000000004</v>
+      </c>
+      <c r="H32" s="183">
+        <f>G32/C32*'Финмодель 6 паллет'!$D$6</f>
+        <v>118.1292</v>
+      </c>
+      <c r="I32" s="174">
+        <f>H32-D32</f>
+        <v>-85.09199999999998</v>
+      </c>
+      <c r="J32" s="175">
+        <f>I32/D32</f>
+        <v>-0.41871615756623815</v>
+      </c>
+      <c r="K32" s="174">
+        <f>H32-E32</f>
+        <v>-116.35679999999999</v>
+      </c>
+      <c r="L32" s="175">
+        <f>K32/E32</f>
+        <v>-0.49622066989073976</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="71">
+      <c r="A33" s="176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B33" s="177" t="str">
+        <f>IF(ABS(A33-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v>◄ поточна</v>
+      </c>
+      <c r="C33" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-A33</f>
+        <v>0.45</v>
+      </c>
+      <c r="D33" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/C33*'Финмодель 6 паллет'!$D$6</f>
+        <v>180.64106666666663</v>
+      </c>
+      <c r="E33" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/C33*'Финмодель 6 паллет'!$D$6</f>
+        <v>208.43200000000002</v>
+      </c>
+      <c r="F33" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*C33/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.32</v>
+      </c>
+      <c r="G33" s="182">
+        <f>(F33*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(F33+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(F33+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>38.15951999999999</v>
+      </c>
+      <c r="H33" s="183">
+        <f>G33/C33*'Финмодель 6 паллет'!$D$6</f>
+        <v>118.71850666666664</v>
+      </c>
+      <c r="I33" s="174">
+        <f>H33-D33</f>
+        <v>-61.92255999999999</v>
+      </c>
+      <c r="J33" s="175">
+        <f>I33/D33</f>
+        <v>-0.342793369983053</v>
+      </c>
+      <c r="K33" s="174">
+        <f>H33-E33</f>
+        <v>-89.71349333333337</v>
+      </c>
+      <c r="L33" s="175">
+        <f>K33/E33</f>
+        <v>-0.4304209206519794</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="71">
+      <c r="A34" s="176" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B34" s="177" t="str">
+        <f>IF(ABS(A34-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C34" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-A34</f>
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/C34*'Финмодель 6 паллет'!$D$6</f>
+        <v>162.57695999999999</v>
+      </c>
+      <c r="E34" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/C34*'Финмодель 6 паллет'!$D$6</f>
+        <v>187.58880000000002</v>
+      </c>
+      <c r="F34" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*C34/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="G34" s="182">
+        <f>(F34*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(F34+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(F34+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>42.56784</v>
+      </c>
+      <c r="H34" s="183">
+        <f>G34/C34*'Финмодель 6 паллет'!$D$6</f>
+        <v>119.18995199999998</v>
+      </c>
+      <c r="I34" s="174">
+        <f>H34-D34</f>
+        <v>-43.38700800000001</v>
+      </c>
+      <c r="J34" s="175">
+        <f>I34/D34</f>
+        <v>-0.26687058239986783</v>
+      </c>
+      <c r="K34" s="174">
+        <f>H34-E34</f>
+        <v>-68.39884800000004</v>
+      </c>
+      <c r="L34" s="175">
+        <f>K34/E34</f>
+        <v>-0.36462117141321887</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="71">
+      <c r="A35" s="176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B35" s="177" t="str">
+        <f>IF(ABS(A35-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C35" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-A35</f>
+        <v>0.55</v>
+      </c>
+      <c r="D35" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/C35*'Финмодель 6 паллет'!$D$6</f>
+        <v>147.79723636363633</v>
+      </c>
+      <c r="E35" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/C35*'Финмодель 6 паллет'!$D$6</f>
+        <v>170.5352727272727</v>
+      </c>
+      <c r="F35" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*C35/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.46</v>
+      </c>
+      <c r="G35" s="182">
+        <f>(F35*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(F35+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(F35+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>46.97616</v>
+      </c>
+      <c r="H35" s="183">
+        <f>G35/C35*'Финмодель 6 паллет'!$D$6</f>
+        <v>119.57567999999998</v>
+      </c>
+      <c r="I35" s="174">
+        <f>H35-D35</f>
+        <v>-28.221556363636353</v>
+      </c>
+      <c r="J35" s="175">
+        <f>I35/D35</f>
+        <v>-0.19094779481668248</v>
+      </c>
+      <c r="K35" s="174">
+        <f>H35-E35</f>
+        <v>-50.959592727272735</v>
+      </c>
+      <c r="L35" s="175">
+        <f>K35/E35</f>
+        <v>-0.29882142217445823</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="71">
+      <c r="A36" s="176" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B36" s="177" t="str">
+        <f>IF(ABS(A36-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C36" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-A36</f>
+        <v>0.6</v>
+      </c>
+      <c r="D36" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/C36*'Финмодель 6 паллет'!$D$6</f>
+        <v>135.4808</v>
+      </c>
+      <c r="E36" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/C36*'Финмодель 6 паллет'!$D$6</f>
+        <v>156.324</v>
+      </c>
+      <c r="F36" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*C36/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.53</v>
+      </c>
+      <c r="G36" s="182">
+        <f>(F36*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(F36+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(F36+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>51.38448</v>
+      </c>
+      <c r="H36" s="183">
+        <f>G36/C36*'Финмодель 6 паллет'!$D$6</f>
+        <v>119.89712000000002</v>
+      </c>
+      <c r="I36" s="174">
+        <f>H36-D36</f>
+        <v>-15.583679999999973</v>
+      </c>
+      <c r="J36" s="175">
+        <f>I36/D36</f>
+        <v>-0.1150250072334971</v>
+      </c>
+      <c r="K36" s="174">
+        <f>H36-E36</f>
+        <v>-36.42688</v>
+      </c>
+      <c r="L36" s="175">
+        <f>K36/E36</f>
+        <v>-0.23302167293569762</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" s="71">
+      <c r="A37" s="176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B37" s="177" t="str">
+        <f>IF(ABS(A37-'Цена 120 грн — 6 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C37" s="178">
+        <f>1-'Финмодель 6 паллет'!$D$4-A37</f>
+        <v>0.65</v>
+      </c>
+      <c r="D37" s="179">
+        <f>'Финмодель 6 паллет'!$F$13/C37*'Финмодель 6 паллет'!$D$6</f>
+        <v>125.05919999999998</v>
+      </c>
+      <c r="E37" s="180">
+        <f>'Финмодель 6 паллет'!$F$11/C37*'Финмодель 6 паллет'!$D$6</f>
+        <v>144.29907692307694</v>
+      </c>
+      <c r="F37" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 6 паллет'!$B$14/'Цена 120 грн — 6 паллет'!$E$14*C37/(1+0))/'Финмодель 6 паллет'!$D$3/(1+0.025)-(2600+288+42+2600*0.7*(0+0.2*(1+0)))/9600)/((1+0)*(1+0.2)),2)</f>
+        <v>0.59</v>
+      </c>
+      <c r="G37" s="182">
+        <f>(F37*'Финмодель 6 паллет'!$D$3+(2600+288+42)/9600*'Финмодель 6 паллет'!$D$3+(F37+2600*0.7/9600)*0*'Финмодель 6 паллет'!$D$3+(F37+2600*0.7/9600)*(1+0)*0.2*'Финмодель 6 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>55.163039999999995</v>
+      </c>
+      <c r="H37" s="183">
+        <f>G37/C37*'Финмодель 6 паллет'!$D$6</f>
+        <v>118.81270153846151</v>
+      </c>
+      <c r="I37" s="174">
+        <f>H37-D37</f>
+        <v>-6.246498461538465</v>
+      </c>
+      <c r="J37" s="175">
+        <f>I37/D37</f>
+        <v>-0.04994833216219571</v>
+      </c>
+      <c r="K37" s="174">
+        <f>H37-E37</f>
+        <v>-25.486375384615428</v>
+      </c>
+      <c r="L37" s="175">
+        <f>K37/E37</f>
+        <v>-0.1766218878739032</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A29:L29"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:L30"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A6:A7"/>
@@ -7536,7 +8814,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H42" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:L57" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7548,12 +8826,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="38" customWidth="1" style="71" min="1" max="1"/>
     <col width="17" customWidth="1" style="71" min="2" max="8"/>
-    <col width="2" customWidth="1" style="71" min="9" max="9"/>
+    <col width="14" customWidth="1" style="71" min="9" max="9"/>
+    <col width="14" customWidth="1" style="71" min="10" max="10"/>
+    <col width="14" customWidth="1" style="71" min="11" max="11"/>
+    <col width="14" customWidth="1" style="71" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8007,14 +9288,408 @@
         <v>38.52747636363637</v>
       </c>
     </row>
+    <row r="28" ht="26" customHeight="1" s="71">
+      <c r="A28" s="152" t="inlineStr">
+        <is>
+          <t>СЦЕНАРІЇ МАРЖІ · ДО та ПІСЛЯ запиту SIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="71">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>Для кожної маржі: полиця при поточній закупівлі (ДО) і закупівля, яку має прийняти SIAS, щоб полиця була 120 ₴ (ПІСЛЯ). Бонус мережі та націнка — як на аркуші «Цена 120 грн».</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" s="71">
+      <c r="D30" s="154" t="inlineStr">
+        <is>
+          <t>ДО · поточна закупівля</t>
+        </is>
+      </c>
+      <c r="E30" s="154" t="n"/>
+      <c r="F30" s="155" t="inlineStr">
+        <is>
+          <t>ПІСЛЯ · запит для полиці 120 ₴</t>
+        </is>
+      </c>
+      <c r="G30" s="155" t="n"/>
+      <c r="H30" s="155" t="n"/>
+      <c r="I30" s="156" t="inlineStr">
+        <is>
+          <t>ЗМІНА відносно ДО</t>
+        </is>
+      </c>
+      <c r="J30" s="156" t="n"/>
+      <c r="K30" s="156" t="n"/>
+      <c r="L30" s="156" t="n"/>
+    </row>
+    <row r="31" ht="38" customHeight="1" s="71">
+      <c r="A31" s="157" t="inlineStr">
+        <is>
+          <t>Маржа</t>
+        </is>
+      </c>
+      <c r="B31" s="157" t="inlineStr"/>
+      <c r="C31" s="157" t="inlineStr">
+        <is>
+          <t>Частка ціни на СС</t>
+        </is>
+      </c>
+      <c r="D31" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="E31" s="158" t="inlineStr">
+        <is>
+          <t>Полиця 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="F31" s="159" t="inlineStr">
+        <is>
+          <t>Запит, €/пач.</t>
+        </is>
+      </c>
+      <c r="G31" s="159" t="inlineStr">
+        <is>
+          <t>СС, ₴</t>
+        </is>
+      </c>
+      <c r="H31" s="159" t="inlineStr">
+        <is>
+          <t>Полиця, ₴</t>
+        </is>
+      </c>
+      <c r="I31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="J31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 4 SKU, %</t>
+        </is>
+      </c>
+      <c r="K31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, ₴</t>
+        </is>
+      </c>
+      <c r="L31" s="160" t="inlineStr">
+        <is>
+          <t>Δ 2 SKU, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1" s="71">
+      <c r="A32" s="176" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="B32" s="177" t="str">
+        <f>IF(ABS(A32-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C32" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-A32</f>
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/C32*'Финмодель 33 паллет'!$D$6</f>
+        <v>158.12255579868716</v>
+      </c>
+      <c r="E32" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/C32*'Финмодель 33 паллет'!$D$6</f>
+        <v>182.44910284463887</v>
+      </c>
+      <c r="F32" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*C32/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="G32" s="182">
+        <f>(F32*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(F32+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(F32+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>34.11915636363636</v>
+      </c>
+      <c r="H32" s="183">
+        <f>G32/C32*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.41704727272723</v>
+      </c>
+      <c r="I32" s="174">
+        <f>H32-D32</f>
+        <v>-38.70550852595993</v>
+      </c>
+      <c r="J32" s="175">
+        <f>I32/D32</f>
+        <v>-0.24478170322036552</v>
+      </c>
+      <c r="K32" s="174">
+        <f>H32-E32</f>
+        <v>-63.03205557191164</v>
+      </c>
+      <c r="L32" s="175">
+        <f>K32/E32</f>
+        <v>-0.34547747612431623</v>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1" s="71">
+      <c r="A33" s="176" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B33" s="177" t="str">
+        <f>IF(ABS(A33-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v>◄ поточна</v>
+      </c>
+      <c r="C33" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-A33</f>
+        <v>0.45</v>
+      </c>
+      <c r="D33" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/C33*'Финмодель 33 паллет'!$D$6</f>
+        <v>140.55338293216636</v>
+      </c>
+      <c r="E33" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/C33*'Финмодель 33 паллет'!$D$6</f>
+        <v>162.17698030634565</v>
+      </c>
+      <c r="F33" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*C33/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.54</v>
+      </c>
+      <c r="G33" s="182">
+        <f>(F33*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(F33+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(F33+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>38.52747636363637</v>
+      </c>
+      <c r="H33" s="183">
+        <f>G33/C33*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.8632597979798</v>
+      </c>
+      <c r="I33" s="174">
+        <f>H33-D33</f>
+        <v>-20.690123134186564</v>
+      </c>
+      <c r="J33" s="175">
+        <f>I33/D33</f>
+        <v>-0.14720473248354327</v>
+      </c>
+      <c r="K33" s="174">
+        <f>H33-E33</f>
+        <v>-42.31372050836586</v>
+      </c>
+      <c r="L33" s="175">
+        <f>K33/E33</f>
+        <v>-0.2609107681524035</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1" s="71">
+      <c r="A34" s="176" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B34" s="177" t="str">
+        <f>IF(ABS(A34-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C34" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-A34</f>
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/C34*'Финмодель 33 паллет'!$D$6</f>
+        <v>126.49804463894974</v>
+      </c>
+      <c r="E34" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/C34*'Финмодель 33 паллет'!$D$6</f>
+        <v>145.95928227571108</v>
+      </c>
+      <c r="F34" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*C34/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.6</v>
+      </c>
+      <c r="G34" s="182">
+        <f>(F34*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(F34+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(F34+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>42.30603636363636</v>
+      </c>
+      <c r="H34" s="183">
+        <f>G34/C34*'Финмодель 33 паллет'!$D$6</f>
+        <v>118.45690181818179</v>
+      </c>
+      <c r="I34" s="174">
+        <f>H34-D34</f>
+        <v>-8.041142820767945</v>
+      </c>
+      <c r="J34" s="175">
+        <f>I34/D34</f>
+        <v>-0.06356732899483898</v>
+      </c>
+      <c r="K34" s="174">
+        <f>H34-E34</f>
+        <v>-27.502380457529284</v>
+      </c>
+      <c r="L34" s="175">
+        <f>K34/E34</f>
+        <v>-0.1884250184621929</v>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1" s="71">
+      <c r="A35" s="176" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B35" s="177" t="str">
+        <f>IF(ABS(A35-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C35" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-A35</f>
+        <v>0.55</v>
+      </c>
+      <c r="D35" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/C35*'Финмодель 33 паллет'!$D$6</f>
+        <v>114.9982223990452</v>
+      </c>
+      <c r="E35" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/C35*'Финмодель 33 паллет'!$D$6</f>
+        <v>132.6902566142828</v>
+      </c>
+      <c r="F35" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*C35/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.67</v>
+      </c>
+      <c r="G35" s="182">
+        <f>(F35*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(F35+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(F35+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>46.71435636363636</v>
+      </c>
+      <c r="H35" s="183">
+        <f>G35/C35*'Финмодель 33 паллет'!$D$6</f>
+        <v>118.90927074380163</v>
+      </c>
+      <c r="I35" s="174">
+        <f>H35-D35</f>
+        <v>3.9110483447564235</v>
+      </c>
+      <c r="J35" s="175">
+        <f>I35/D35</f>
+        <v>0.0340096417419831</v>
+      </c>
+      <c r="K35" s="174">
+        <f>H35-E35</f>
+        <v>-13.78098587048116</v>
+      </c>
+      <c r="L35" s="175">
+        <f>K35/E35</f>
+        <v>-0.10385831049028037</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1" s="71">
+      <c r="A36" s="176" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B36" s="177" t="str">
+        <f>IF(ABS(A36-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C36" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-A36</f>
+        <v>0.6</v>
+      </c>
+      <c r="D36" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/C36*'Финмодель 33 паллет'!$D$6</f>
+        <v>105.41503719912478</v>
+      </c>
+      <c r="E36" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/C36*'Финмодель 33 паллет'!$D$6</f>
+        <v>121.63273522975923</v>
+      </c>
+      <c r="F36" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*C36/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.74</v>
+      </c>
+      <c r="G36" s="182">
+        <f>(F36*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(F36+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(F36+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>51.12267636363635</v>
+      </c>
+      <c r="H36" s="183">
+        <f>G36/C36*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.28624484848483</v>
+      </c>
+      <c r="I36" s="174">
+        <f>H36-D36</f>
+        <v>13.871207649360045</v>
+      </c>
+      <c r="J36" s="175">
+        <f>I36/D36</f>
+        <v>0.131586612478805</v>
+      </c>
+      <c r="K36" s="174">
+        <f>H36-E36</f>
+        <v>-2.346490381274407</v>
+      </c>
+      <c r="L36" s="175">
+        <f>K36/E36</f>
+        <v>-0.019291602518367965</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1" s="71">
+      <c r="A37" s="176" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B37" s="177" t="str">
+        <f>IF(ABS(A37-'Цена 120 грн — 33 паллет'!$C$14)&lt;0.0000001,"◄ поточна","")</f>
+        <v/>
+      </c>
+      <c r="C37" s="178">
+        <f>1-'Финмодель 33 паллет'!$D$4-A37</f>
+        <v>0.65</v>
+      </c>
+      <c r="D37" s="179">
+        <f>'Финмодель 33 паллет'!$F$13/C37*'Финмодель 33 паллет'!$D$6</f>
+        <v>97.30618818380749</v>
+      </c>
+      <c r="E37" s="180">
+        <f>'Финмодель 33 паллет'!$F$11/C37*'Финмодель 33 паллет'!$D$6</f>
+        <v>112.27637098131622</v>
+      </c>
+      <c r="F37" s="181">
+        <f>ROUNDDOWN((('Цена 120 грн — 33 паллет'!$B$14/'Цена 120 грн — 33 паллет'!$E$14*C37/(1+0))/'Финмодель 33 паллет'!$D$3/(1+0.025)-(3700+288+42+3700*0.7*(0+0.2*(1+0)))/52800)/((1+0)*(1+0.2)),2)</f>
+        <v>0.81</v>
+      </c>
+      <c r="G37" s="182">
+        <f>(F37*'Финмодель 33 паллет'!$D$3+(3700+288+42)/52800*'Финмодель 33 паллет'!$D$3+(F37+3700*0.7/52800)*0*'Финмодель 33 паллет'!$D$3+(F37+3700*0.7/52800)*(1+0)*0.2*'Финмодель 33 паллет'!$D$3)*(1+0.025)*(1+0)</f>
+        <v>55.53099636363637</v>
+      </c>
+      <c r="H37" s="183">
+        <f>G37/C37*'Финмодель 33 паллет'!$D$6</f>
+        <v>119.60522293706295</v>
+      </c>
+      <c r="I37" s="174">
+        <f>H37-D37</f>
+        <v>22.299034753255455</v>
+      </c>
+      <c r="J37" s="175">
+        <f>I37/D37</f>
+        <v>0.22916358321562727</v>
+      </c>
+      <c r="K37" s="174">
+        <f>H37-E37</f>
+        <v>7.328851955746728</v>
+      </c>
+      <c r="L37" s="175">
+        <f>K37/E37</f>
+        <v>0.06527510545354476</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="14">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="A29:L29"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:L30"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A6:A7"/>
@@ -8022,7 +9697,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H41" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
+    <ignoredError sqref="A1:L57" evalError="1" formula="1" formulaRange="1" unlockedFormula="1" numberStoredAsText="1" emptyCellReference="1" twoDigitTextYear="1" listDataValidation="1" calculatedColumn="1"/>
   </ignoredErrors>
 </worksheet>
 </file>